--- a/database/event/5435/event_5435_evp_summary.xlsx
+++ b/database/event/5435/event_5435_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.4037</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4304</v>
+        <v>2.3684</v>
       </c>
       <c r="E2" t="n">
         <v>7.0591</v>
@@ -548,7 +548,7 @@
         <v>1.338</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2969</v>
+        <v>2.2368</v>
       </c>
       <c r="E3" t="n">
         <v>6.7287</v>
@@ -594,7 +594,7 @@
         <v>1.2633</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1451</v>
+        <v>2.0871</v>
       </c>
       <c r="E4" t="n">
         <v>6.353</v>
@@ -640,7 +640,7 @@
         <v>0.9177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.443</v>
+        <v>1.3947</v>
       </c>
       <c r="E5" t="n">
         <v>4.615</v>
@@ -686,7 +686,7 @@
         <v>0.8401</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2852</v>
+        <v>1.2391</v>
       </c>
       <c r="E6" t="n">
         <v>4.2245</v>
@@ -732,7 +732,7 @@
         <v>0.7721</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1472</v>
+        <v>1.103</v>
       </c>
       <c r="E7" t="n">
         <v>3.8828</v>
@@ -778,7 +778,7 @@
         <v>0.7523</v>
       </c>
       <c r="D8" t="n">
-        <v>1.107</v>
+        <v>1.0633</v>
       </c>
       <c r="E8" t="n">
         <v>3.7832</v>
@@ -824,7 +824,7 @@
         <v>0.7389</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0797</v>
+        <v>1.0364</v>
       </c>
       <c r="E9" t="n">
         <v>3.7157</v>
@@ -870,7 +870,7 @@
         <v>0.725</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0516</v>
+        <v>1.0087</v>
       </c>
       <c r="E10" t="n">
         <v>3.6461</v>
@@ -916,7 +916,7 @@
         <v>0.6965</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9936</v>
+        <v>0.9515</v>
       </c>
       <c r="E11" t="n">
         <v>3.5026</v>
@@ -962,7 +962,7 @@
         <v>0.5135999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.622</v>
+        <v>0.5851</v>
       </c>
       <c r="E12" t="n">
         <v>2.5828</v>
@@ -1008,7 +1008,7 @@
         <v>0.4538</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5006</v>
+        <v>0.4653</v>
       </c>
       <c r="E13" t="n">
         <v>2.2821</v>
@@ -1054,7 +1054,7 @@
         <v>0.4182</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4283</v>
+        <v>0.394</v>
       </c>
       <c r="E14" t="n">
         <v>2.1032</v>
@@ -1100,7 +1100,7 @@
         <v>0.411</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4135</v>
+        <v>0.3795</v>
       </c>
       <c r="E15" t="n">
         <v>2.0667</v>
@@ -1146,7 +1146,7 @@
         <v>0.3774</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3453</v>
+        <v>0.3121</v>
       </c>
       <c r="E16" t="n">
         <v>1.8977</v>
@@ -1192,7 +1192,7 @@
         <v>0.3522</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2941</v>
+        <v>0.2617</v>
       </c>
       <c r="E17" t="n">
         <v>1.7711</v>
@@ -1238,7 +1238,7 @@
         <v>0.3404</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2702</v>
+        <v>0.2381</v>
       </c>
       <c r="E18" t="n">
         <v>1.7119</v>
@@ -1284,7 +1284,7 @@
         <v>0.3105</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2094</v>
+        <v>0.1782</v>
       </c>
       <c r="E19" t="n">
         <v>1.5614</v>
@@ -1330,7 +1330,7 @@
         <v>0.302</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1921</v>
+        <v>0.1611</v>
       </c>
       <c r="E20" t="n">
         <v>1.5185</v>
@@ -1376,7 +1376,7 @@
         <v>0.2904</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1685</v>
+        <v>0.1378</v>
       </c>
       <c r="E21" t="n">
         <v>1.4602</v>
@@ -1422,7 +1422,7 @@
         <v>0.2551</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0968</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>1.2827</v>
@@ -1468,7 +1468,7 @@
         <v>0.2265</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0387</v>
+        <v>0.0098</v>
       </c>
       <c r="E23" t="n">
         <v>1.1388</v>
@@ -1514,7 +1514,7 @@
         <v>0.2263</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0384</v>
+        <v>0.0095</v>
       </c>
       <c r="E24" t="n">
         <v>1.138</v>
@@ -1560,7 +1560,7 @@
         <v>0.2065</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0018</v>
+        <v>-0.0302</v>
       </c>
       <c r="E25" t="n">
         <v>1.0385</v>
@@ -1606,7 +1606,7 @@
         <v>0.1692</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0776</v>
+        <v>-0.1049</v>
       </c>
       <c r="E26" t="n">
         <v>0.851</v>
@@ -1652,7 +1652,7 @@
         <v>0.1099</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1981</v>
+        <v>-0.2237</v>
       </c>
       <c r="E27" t="n">
         <v>0.5527</v>
@@ -1698,7 +1698,7 @@
         <v>0.1049</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2083</v>
+        <v>-0.2338</v>
       </c>
       <c r="E28" t="n">
         <v>0.5273</v>
@@ -1744,7 +1744,7 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.224</v>
+        <v>-0.2493</v>
       </c>
       <c r="E29" t="n">
         <v>0.4886</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0025</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4264</v>
+        <v>-0.4489</v>
       </c>
       <c r="E30" t="n">
         <v>-0.0124</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0276</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4774</v>
+        <v>-0.4991</v>
       </c>
       <c r="E31" t="n">
         <v>-0.1386</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1064</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6375</v>
+        <v>-0.657</v>
       </c>
       <c r="E32" t="n">
         <v>-0.5349</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1604</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7472</v>
+        <v>-0.7652</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8065</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1642</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7549</v>
+        <v>-0.7729</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8257</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1705</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7677</v>
+        <v>-0.7854</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8572</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1869</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.801</v>
+        <v>-0.8183</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9398</v>
@@ -2112,7 +2112,7 @@
         <v>-0.24</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.9247</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2067</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3139</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0591</v>
+        <v>-1.0729</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5787</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3461</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1244</v>
+        <v>-1.1372</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7403</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3977</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E40" t="n">
         <v>-2</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6475</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7368</v>
+        <v>-1.7412</v>
       </c>
       <c r="E41" t="n">
         <v>-3.2562</v>

--- a/database/event/5435/event_5435_evp_summary.xlsx
+++ b/database/event/5435/event_5435_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0591</v>
+        <v>6.2216</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4037</v>
+        <v>1.2372</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3684</v>
+        <v>2.1707</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0591</v>
+        <v>6.2216</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8073</v>
+        <v>3.9367</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2518</v>
+        <v>2.2849</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8073</v>
+        <v>8.3842</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0859</v>
+        <v>4.3594</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2518</v>
+        <v>2.2849</v>
       </c>
       <c r="K2" t="n">
         <v>91</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3377</v>
+        <v>6.644299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7287</v>
+        <v>6.2031</v>
       </c>
       <c r="C3" t="n">
-        <v>1.338</v>
+        <v>1.2335</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2368</v>
+        <v>2.1624</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7287</v>
+        <v>6.2031</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3385</v>
+        <v>3.4042</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3902</v>
+        <v>2.7989</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8944</v>
+        <v>6.5079</v>
       </c>
       <c r="I3" t="n">
-        <v>3.967</v>
+        <v>3.3838</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3902</v>
+        <v>2.7989</v>
       </c>
       <c r="K3" t="n">
         <v>91</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>6.357200000000001</v>
+        <v>6.182700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.353</v>
+        <v>6.0185</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2633</v>
+        <v>1.1968</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0871</v>
+        <v>2.079</v>
       </c>
       <c r="E4" t="n">
-        <v>6.353</v>
+        <v>6.0185</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9067</v>
+        <v>3.0464</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4463</v>
+        <v>2.9721</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9067</v>
+        <v>5.2474</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3559</v>
+        <v>2.7284</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4463</v>
+        <v>2.9721</v>
       </c>
       <c r="K4" t="n">
         <v>195</v>
@@ -621,7 +621,7 @@
         <v>191</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8022</v>
+        <v>5.7005</v>
       </c>
       <c r="N4" t="n">
         <v>386</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.615</v>
+        <v>5.9173</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9177</v>
+        <v>1.1767</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3947</v>
+        <v>2.0334</v>
       </c>
       <c r="E5" t="n">
-        <v>4.615</v>
+        <v>5.9173</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5178</v>
+        <v>1.7761</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0972</v>
+        <v>4.1412</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5178</v>
+        <v>1.7761</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4197</v>
+        <v>0.9235</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0972</v>
+        <v>4.1412</v>
       </c>
       <c r="K5" t="n">
         <v>195</v>
@@ -667,7 +667,7 @@
         <v>191</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5169</v>
+        <v>5.0647</v>
       </c>
       <c r="N5" t="n">
         <v>386</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2245</v>
+        <v>4.5413</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8401</v>
+        <v>0.9031</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2391</v>
+        <v>1.4122</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2245</v>
+        <v>4.5413</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0725</v>
+        <v>2.5796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.152</v>
+        <v>1.9617</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0725</v>
+        <v>3.6026</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3008</v>
+        <v>1.8732</v>
       </c>
       <c r="J6" t="n">
-        <v>0.152</v>
+        <v>1.9617</v>
       </c>
       <c r="K6" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>191</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4528</v>
+        <v>3.8349</v>
       </c>
       <c r="N6" t="n">
-        <v>245</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8828</v>
+        <v>4.0173</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7721</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.103</v>
+        <v>1.1756</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8828</v>
+        <v>4.0173</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0736</v>
+        <v>3.4851</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8092</v>
+        <v>0.5322</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0736</v>
+        <v>6.7929</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6807</v>
+        <v>3.532</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8092</v>
+        <v>0.5322</v>
       </c>
       <c r="K7" t="n">
         <v>195</v>
@@ -759,7 +759,7 @@
         <v>191</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4899</v>
+        <v>4.0642</v>
       </c>
       <c r="N7" t="n">
         <v>386</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7832</v>
+        <v>3.952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7523</v>
+        <v>0.7859</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0633</v>
+        <v>1.1461</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7832</v>
+        <v>3.952</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8163</v>
+        <v>2.9404</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9669</v>
+        <v>1.0116</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8163</v>
+        <v>4.8739</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2827</v>
+        <v>2.5342</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9669</v>
+        <v>1.0116</v>
       </c>
       <c r="K8" t="n">
         <v>91</v>
@@ -805,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2496</v>
+        <v>3.5458</v>
       </c>
       <c r="N8" t="n">
         <v>281</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7157</v>
+        <v>3.8252</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7389</v>
+        <v>0.7607</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0364</v>
+        <v>1.0889</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7157</v>
+        <v>3.8252</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6068</v>
+        <v>3.6309</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1089</v>
+        <v>0.1943</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6068</v>
+        <v>7.3066</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9234</v>
+        <v>3.7991</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1089</v>
+        <v>0.1943</v>
       </c>
       <c r="K9" t="n">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="L9" t="n">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0323</v>
+        <v>3.9934</v>
       </c>
       <c r="N9" t="n">
-        <v>281</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6461</v>
+        <v>3.6238</v>
       </c>
       <c r="C10" t="n">
-        <v>0.725</v>
+        <v>0.7206</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0087</v>
+        <v>0.998</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6461</v>
+        <v>3.6238</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1022</v>
+        <v>3.4095</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4561</v>
+        <v>0.2143</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1022</v>
+        <v>6.5267</v>
       </c>
       <c r="I10" t="n">
-        <v>3.325</v>
+        <v>3.3936</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4561</v>
+        <v>0.2143</v>
       </c>
       <c r="K10" t="n">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8689</v>
+        <v>3.6079</v>
       </c>
       <c r="N10" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5026</v>
+        <v>3.4152</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6965</v>
+        <v>0.6791</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9515</v>
+        <v>0.9038</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5026</v>
+        <v>3.4152</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3575</v>
+        <v>2.5282</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1451</v>
+        <v>0.887</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3575</v>
+        <v>3.4216</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7213</v>
+        <v>1.7791</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1451</v>
+        <v>0.887</v>
       </c>
       <c r="K11" t="n">
         <v>195</v>
@@ -943,7 +943,7 @@
         <v>191</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8664</v>
+        <v>2.6661</v>
       </c>
       <c r="N11" t="n">
         <v>386</v>
@@ -952,173 +952,173 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5828</v>
+        <v>3.201</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5851</v>
+        <v>0.8071</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5828</v>
+        <v>3.201</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7728</v>
+        <v>3.5137</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.3127</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7728</v>
+        <v>6.8939</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4369</v>
+        <v>3.5845</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.3127</v>
       </c>
       <c r="K12" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L12" t="n">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2469</v>
+        <v>3.2718</v>
       </c>
       <c r="N12" t="n">
-        <v>386</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2821</v>
+        <v>2.9717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4538</v>
+        <v>0.5909</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4653</v>
+        <v>0.7036</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2821</v>
+        <v>2.9717</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2821</v>
+        <v>2.5069</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.4648</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2821</v>
+        <v>3.3464</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2821</v>
+        <v>1.74</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.4648</v>
       </c>
       <c r="K13" t="n">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2821</v>
+        <v>2.2048</v>
       </c>
       <c r="N13" t="n">
-        <v>222</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1032</v>
+        <v>2.6262</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4182</v>
+        <v>0.5222</v>
       </c>
       <c r="D14" t="n">
-        <v>0.394</v>
+        <v>0.5476</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1032</v>
+        <v>2.6262</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4783</v>
+        <v>2.6804</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3751</v>
+        <v>-0.0542</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4783</v>
+        <v>3.9578</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0087</v>
+        <v>2.0579</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3751</v>
+        <v>-0.0542</v>
       </c>
       <c r="K14" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="L14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6336</v>
+        <v>2.0037</v>
       </c>
       <c r="N14" t="n">
-        <v>198</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0667</v>
+        <v>2.5263</v>
       </c>
       <c r="C15" t="n">
-        <v>0.411</v>
+        <v>0.5024</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3795</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0667</v>
+        <v>2.5263</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9549</v>
+        <v>2.7511</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8882</v>
+        <v>-0.2248</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9549</v>
+        <v>4.2067</v>
       </c>
       <c r="I15" t="n">
-        <v>2.395</v>
+        <v>2.1873</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8882</v>
+        <v>-0.2248</v>
       </c>
       <c r="K15" t="n">
         <v>145</v>
@@ -1127,7 +1127,7 @@
         <v>53</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5068</v>
+        <v>1.9625</v>
       </c>
       <c r="N15" t="n">
         <v>198</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8977</v>
+        <v>2.3287</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3774</v>
+        <v>0.4631</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3121</v>
+        <v>0.4133</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8977</v>
+        <v>2.3287</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8977</v>
+        <v>2.3287</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8977</v>
+        <v>2.3287</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8977</v>
+        <v>2.3287</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8977</v>
+        <v>2.3287</v>
       </c>
       <c r="N16" t="n">
         <v>222</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7711</v>
+        <v>2.3064</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3522</v>
+        <v>0.4586</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2617</v>
+        <v>0.4032</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7711</v>
+        <v>2.3064</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2987</v>
+        <v>2.2781</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4724</v>
+        <v>0.0283</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2987</v>
+        <v>2.5402</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0526</v>
+        <v>1.3208</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4724</v>
+        <v>0.0283</v>
       </c>
       <c r="K17" t="n">
         <v>193</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.525</v>
+        <v>1.3491</v>
       </c>
       <c r="N17" t="n">
         <v>245</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>leaf</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7119</v>
+        <v>2.2643</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3404</v>
+        <v>0.4503</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2381</v>
+        <v>0.3842</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7119</v>
+        <v>2.2643</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1859</v>
+        <v>2.8553</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.474</v>
+        <v>-0.591</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1859</v>
+        <v>4.5741</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7717</v>
+        <v>2.3783</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.474</v>
+        <v>-0.591</v>
       </c>
       <c r="K18" t="n">
         <v>145</v>
@@ -1265,7 +1265,7 @@
         <v>53</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2977</v>
+        <v>1.7873</v>
       </c>
       <c r="N18" t="n">
         <v>198</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5614</v>
+        <v>2.2561</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3105</v>
+        <v>0.4486</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1782</v>
+        <v>0.3805</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5614</v>
+        <v>2.2561</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8589</v>
+        <v>2.2561</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2975</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8589</v>
+        <v>2.2561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5067</v>
+        <v>2.2561</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2975</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="L19" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2092</v>
+        <v>2.2561</v>
       </c>
       <c r="N19" t="n">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5185</v>
+        <v>2.2205</v>
       </c>
       <c r="C20" t="n">
-        <v>0.302</v>
+        <v>0.4416</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1611</v>
+        <v>0.3644</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5185</v>
+        <v>2.2205</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5185</v>
+        <v>2.5609</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3404</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5185</v>
+        <v>3.5369</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5185</v>
+        <v>1.839</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3404</v>
       </c>
       <c r="K20" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5185</v>
+        <v>1.4986</v>
       </c>
       <c r="N20" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4602</v>
+        <v>1.923</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2904</v>
+        <v>0.3824</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1378</v>
+        <v>0.2301</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4602</v>
+        <v>1.923</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4602</v>
+        <v>1.923</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4602</v>
+        <v>1.923</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4602</v>
+        <v>1.923</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4602</v>
+        <v>1.923</v>
       </c>
       <c r="N21" t="n">
         <v>222</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>s0m</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2827</v>
+        <v>1.6162</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2551</v>
+        <v>0.3214</v>
       </c>
       <c r="D22" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0916</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2827</v>
+        <v>1.6162</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2827</v>
+        <v>1.6162</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2827</v>
+        <v>1.6162</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2827</v>
+        <v>1.6162</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2827</v>
+        <v>1.6162</v>
       </c>
       <c r="N22" t="n">
-        <v>141</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1388</v>
+        <v>1.611</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2265</v>
+        <v>0.3204</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0098</v>
+        <v>0.0893</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1388</v>
+        <v>1.611</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1388</v>
+        <v>1.611</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1388</v>
+        <v>1.611</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1388</v>
+        <v>1.611</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1388</v>
+        <v>1.611</v>
       </c>
       <c r="N23" t="n">
-        <v>231</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>s0m</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.138</v>
+        <v>1.5775</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2263</v>
+        <v>0.3137</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0095</v>
+        <v>0.0741</v>
       </c>
       <c r="E24" t="n">
-        <v>1.138</v>
+        <v>1.5775</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2259</v>
+        <v>1.5775</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2259</v>
+        <v>1.5775</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9937</v>
+        <v>1.5775</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="L24" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9058</v>
+        <v>1.5775</v>
       </c>
       <c r="N24" t="n">
-        <v>245</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Xeppaa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0385</v>
+        <v>1.4056</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2065</v>
+        <v>0.2795</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0302</v>
+        <v>-0.0035</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0385</v>
+        <v>1.4056</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0385</v>
+        <v>1.699</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.2934</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0385</v>
+        <v>1.699</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0385</v>
+        <v>0.8834</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.2934</v>
       </c>
       <c r="K25" t="n">
-        <v>231</v>
+        <v>145</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0385</v>
+        <v>0.59</v>
       </c>
       <c r="N25" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.851</v>
+        <v>1.3299</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1692</v>
+        <v>0.2645</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1049</v>
+        <v>-0.0376</v>
       </c>
       <c r="E26" t="n">
-        <v>0.851</v>
+        <v>1.3299</v>
       </c>
       <c r="F26" t="n">
-        <v>0.851</v>
+        <v>1.3299</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.851</v>
+        <v>1.3299</v>
       </c>
       <c r="I26" t="n">
-        <v>0.851</v>
+        <v>1.3299</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.851</v>
+        <v>1.3299</v>
       </c>
       <c r="N26" t="n">
         <v>222</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5527</v>
+        <v>1.2117</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1099</v>
+        <v>0.241</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2237</v>
+        <v>-0.091</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5527</v>
+        <v>1.2117</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5527</v>
+        <v>1.2117</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5527</v>
+        <v>1.2117</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5527</v>
+        <v>1.2117</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5527</v>
+        <v>1.2117</v>
       </c>
       <c r="N27" t="n">
         <v>231</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5273</v>
+        <v>1.1159</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1049</v>
+        <v>0.2219</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2338</v>
+        <v>-0.1342</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5273</v>
+        <v>1.1159</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5273</v>
+        <v>1.1159</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5273</v>
+        <v>1.1159</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5273</v>
+        <v>1.1159</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5273</v>
+        <v>1.1159</v>
       </c>
       <c r="N28" t="n">
         <v>231</v>
@@ -1734,216 +1734,216 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4886</v>
+        <v>0.8651</v>
       </c>
       <c r="C29" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2493</v>
+        <v>-0.2475</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4886</v>
+        <v>0.8651</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8622</v>
+        <v>0.8651</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3736</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8622</v>
+        <v>0.8651</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6988</v>
+        <v>0.8651</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3736</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3252</v>
+        <v>0.8651</v>
       </c>
       <c r="N29" t="n">
-        <v>198</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>vanity</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0124</v>
+        <v>0.6438</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0025</v>
+        <v>0.128</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4489</v>
+        <v>-0.3474</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0124</v>
+        <v>0.6438</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0124</v>
+        <v>0.926</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.2822</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0124</v>
+        <v>0.926</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0124</v>
+        <v>0.4815</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.2822</v>
       </c>
       <c r="K30" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0124</v>
+        <v>0.1993</v>
       </c>
       <c r="N30" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vanity</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1386</v>
+        <v>0.2552</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0276</v>
+        <v>0.0507</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4991</v>
+        <v>-0.5228</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1386</v>
+        <v>0.2552</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2138</v>
+        <v>0.2552</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3524</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2138</v>
+        <v>0.2552</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1733</v>
+        <v>0.2552</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3524</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L31" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1791</v>
+        <v>0.2552</v>
       </c>
       <c r="N31" t="n">
-        <v>198</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5349</v>
+        <v>0.0083</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1064</v>
+        <v>0.0017</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.657</v>
+        <v>-0.6343</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5349</v>
+        <v>0.0083</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5349</v>
+        <v>0.9787</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.9704</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5349</v>
+        <v>0.9787</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5349</v>
+        <v>0.5089</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.9704</v>
       </c>
       <c r="K32" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5349</v>
+        <v>-0.4615</v>
       </c>
       <c r="N32" t="n">
-        <v>118</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>penny</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8065</v>
+        <v>-0.2598</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1604</v>
+        <v>-0.0517</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7652</v>
+        <v>-0.7553</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8065</v>
+        <v>-0.2598</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8065</v>
+        <v>-0.2598</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8065</v>
+        <v>-0.2598</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8065</v>
+        <v>-0.2598</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8065</v>
+        <v>-0.2598</v>
       </c>
       <c r="N33" t="n">
         <v>118</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8257</v>
+        <v>-0.3616</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1642</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7729</v>
+        <v>-0.8013</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8257</v>
+        <v>-0.3616</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2518</v>
+        <v>-0.3616</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0775</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2518</v>
+        <v>-0.3616</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2041</v>
+        <v>-0.3616</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.0775</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="L34" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8734</v>
+        <v>-0.3616</v>
       </c>
       <c r="N34" t="n">
-        <v>281</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>penny</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8572</v>
+        <v>-0.3933</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1705</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7854</v>
+        <v>-0.8156</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8572</v>
+        <v>-0.3933</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8572</v>
+        <v>-0.3933</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8572</v>
+        <v>-0.3933</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8572</v>
+        <v>-0.3933</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8572</v>
+        <v>-0.3933</v>
       </c>
       <c r="N35" t="n">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9398</v>
+        <v>-0.6223</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1869</v>
+        <v>-0.1237</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8183</v>
+        <v>-0.919</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9398</v>
+        <v>-0.6223</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9398</v>
+        <v>-0.6223</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9398</v>
+        <v>-0.6223</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9398</v>
+        <v>-0.6223</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9398</v>
+        <v>-0.6223</v>
       </c>
       <c r="N36" t="n">
         <v>118</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2067</v>
+        <v>-0.7811</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.24</v>
+        <v>-0.1553</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9247</v>
+        <v>-0.9906</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2067</v>
+        <v>-0.7811</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2067</v>
+        <v>-0.7811</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2067</v>
+        <v>-0.7811</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2067</v>
+        <v>-0.7811</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2067</v>
+        <v>-0.7811</v>
       </c>
       <c r="N37" t="n">
         <v>118</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5787</v>
+        <v>-0.9411</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3139</v>
+        <v>-0.1871</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0729</v>
+        <v>-1.0629</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5787</v>
+        <v>-0.9411</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5787</v>
+        <v>-0.9411</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5787</v>
+        <v>-0.9411</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5787</v>
+        <v>-0.9411</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>141</v>
+        <v>222</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5787</v>
+        <v>-0.9411</v>
       </c>
       <c r="N38" t="n">
-        <v>141</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7403</v>
+        <v>-0.97</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3461</v>
+        <v>-0.1929</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1372</v>
+        <v>-1.0759</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7403</v>
+        <v>-0.97</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7403</v>
+        <v>-0.97</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7403</v>
+        <v>-0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7403</v>
+        <v>-0.97</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7403</v>
+        <v>-0.97</v>
       </c>
       <c r="N39" t="n">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2</v>
+        <v>-1.7809</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3977</v>
+        <v>-0.3541</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2407</v>
+        <v>-1.442</v>
       </c>
       <c r="E40" t="n">
-        <v>-2</v>
+        <v>-1.7809</v>
       </c>
       <c r="F40" t="n">
-        <v>-2</v>
+        <v>-1.7809</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>-1.7809</v>
       </c>
       <c r="I40" t="n">
-        <v>-2</v>
+        <v>-1.7809</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2</v>
+        <v>-1.7809</v>
       </c>
       <c r="N40" t="n">
         <v>118</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2562</v>
+        <v>-2.761</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6475</v>
+        <v>-0.549</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7412</v>
+        <v>-1.8845</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2562</v>
+        <v>-2.761</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2562</v>
+        <v>-2.761</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2562</v>
+        <v>-2.761</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.2562</v>
+        <v>-2.761</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.2562</v>
+        <v>-2.761</v>
       </c>
       <c r="N41" t="n">
         <v>231</v>
@@ -2429,10 +2429,10 @@
         <v>1.27</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4779</v>
+        <v>0.5617</v>
       </c>
       <c r="J2" t="n">
-        <v>16.7265</v>
+        <v>19.6595</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4233</v>
+        <v>0.4906</v>
       </c>
       <c r="J3" t="n">
-        <v>14.8155</v>
+        <v>17.171</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1709</v>
+        <v>0.1819</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9815</v>
+        <v>6.3665</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2637</v>
+        <v>-0.157</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.2295</v>
+        <v>-5.495</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.659</v>
+        <v>-0.4392</v>
       </c>
       <c r="J6" t="n">
-        <v>-23.065</v>
+        <v>-15.372</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8445</v>
+        <v>0.8329</v>
       </c>
       <c r="J7" t="n">
-        <v>29.5575</v>
+        <v>29.1515</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6187</v>
       </c>
       <c r="J8" t="n">
-        <v>21.9625</v>
+        <v>21.6545</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J9" t="n">
-        <v>8.221500000000001</v>
+        <v>10.0135</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1726</v>
+        <v>0.2274</v>
       </c>
       <c r="J10" t="n">
-        <v>6.041</v>
+        <v>7.959</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1075</v>
+        <v>0.1651</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7625</v>
+        <v>5.7785</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.64</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8447</v>
+        <v>0.7631</v>
       </c>
       <c r="J12" t="n">
-        <v>21.1175</v>
+        <v>19.0775</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5693</v>
+        <v>0.505</v>
       </c>
       <c r="J13" t="n">
-        <v>14.2325</v>
+        <v>12.625</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2629</v>
+        <v>0.2655</v>
       </c>
       <c r="J14" t="n">
-        <v>6.5725</v>
+        <v>6.6375</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.073</v>
+        <v>0.1022</v>
       </c>
       <c r="J15" t="n">
-        <v>1.825</v>
+        <v>2.555</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2153</v>
+        <v>-0.1133</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.3825</v>
+        <v>-2.8325</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.21</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4077</v>
+        <v>0.3571</v>
       </c>
       <c r="J17" t="n">
-        <v>10.1925</v>
+        <v>8.9275</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1055</v>
+        <v>0.0745</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6375</v>
+        <v>1.8625</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2526</v>
+        <v>-0.153</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.315</v>
+        <v>-3.825</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4614</v>
+        <v>-0.2947</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.535</v>
+        <v>-7.3675</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.22</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4211</v>
+        <v>0.4843</v>
       </c>
       <c r="J22" t="n">
-        <v>11.7908</v>
+        <v>13.5604</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3488</v>
+        <v>0.3911</v>
       </c>
       <c r="J23" t="n">
-        <v>9.766400000000001</v>
+        <v>10.9508</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2191</v>
+        <v>-0.1314</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.1348</v>
+        <v>-3.6792</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2532</v>
+        <v>-0.1532</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.0896</v>
+        <v>-4.2896</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5154</v>
+        <v>-0.3333</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.4312</v>
+        <v>-9.3324</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2607</v>
+        <v>1.162</v>
       </c>
       <c r="J27" t="n">
-        <v>35.2996</v>
+        <v>32.536</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9029</v>
+        <v>0.8884</v>
       </c>
       <c r="J28" t="n">
-        <v>25.2812</v>
+        <v>24.8752</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.251</v>
+        <v>0.2913</v>
       </c>
       <c r="J29" t="n">
-        <v>7.028</v>
+        <v>8.1564</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4229</v>
+        <v>-0.3545</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.8412</v>
+        <v>-9.926</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7337</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.5436</v>
+        <v>-19.096</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.88</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0461</v>
+        <v>0.963</v>
       </c>
       <c r="J32" t="n">
-        <v>23.0142</v>
+        <v>21.186</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.68</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8413</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>18.5086</v>
+        <v>16.9554</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.41</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5114</v>
+        <v>0.4972</v>
       </c>
       <c r="J34" t="n">
-        <v>11.2508</v>
+        <v>10.9384</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.22</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2612</v>
+        <v>0.2832</v>
       </c>
       <c r="J35" t="n">
-        <v>5.7464</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2226</v>
+        <v>-0.1162</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.8972</v>
+        <v>-2.5564</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.02</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1832</v>
+        <v>0.124</v>
       </c>
       <c r="J37" t="n">
-        <v>4.0304</v>
+        <v>2.728</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.86</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1585</v>
+        <v>-0.143</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.487</v>
+        <v>-3.146</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2245</v>
+        <v>-0.1862</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.939</v>
+        <v>-4.0964</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.76</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3245</v>
+        <v>-0.2464</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.139</v>
+        <v>-5.4208</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.21</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0619</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-23.3618</v>
+        <v>-16.621</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.7</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9442</v>
+        <v>1.1232</v>
       </c>
       <c r="J42" t="n">
-        <v>26.4376</v>
+        <v>31.4496</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2027</v>
+        <v>0.2636</v>
       </c>
       <c r="J43" t="n">
-        <v>5.6756</v>
+        <v>7.3808</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1327</v>
+        <v>-0.0623</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.7156</v>
+        <v>-1.7444</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.96</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.153</v>
+        <v>-0.0757</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.284</v>
+        <v>-2.1196</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3212</v>
+        <v>-0.1908</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.993600000000001</v>
+        <v>-5.3424</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2389</v>
+        <v>1.1454</v>
       </c>
       <c r="J47" t="n">
-        <v>34.6892</v>
+        <v>32.0712</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4197</v>
+        <v>0.3884</v>
       </c>
       <c r="J48" t="n">
-        <v>11.7516</v>
+        <v>10.8752</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3901</v>
+        <v>0.3608</v>
       </c>
       <c r="J49" t="n">
-        <v>10.9228</v>
+        <v>10.1024</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5064</v>
+        <v>-0.4488</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.1792</v>
+        <v>-12.5664</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9428</v>
+        <v>-0.9129</v>
       </c>
       <c r="J51" t="n">
-        <v>-26.3984</v>
+        <v>-25.5612</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.28</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8282</v>
+        <v>0.6075</v>
       </c>
       <c r="J52" t="n">
-        <v>21.5332</v>
+        <v>15.795</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2219</v>
+        <v>0.2161</v>
       </c>
       <c r="J53" t="n">
-        <v>5.7694</v>
+        <v>5.6186</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0537</v>
+        <v>0.0837</v>
       </c>
       <c r="J54" t="n">
-        <v>1.3962</v>
+        <v>2.1762</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0537</v>
+        <v>0.0837</v>
       </c>
       <c r="J55" t="n">
-        <v>1.3962</v>
+        <v>2.1762</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4519</v>
+        <v>-0.3931</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.7494</v>
+        <v>-10.2206</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4116</v>
+        <v>0.4235</v>
       </c>
       <c r="J57" t="n">
-        <v>10.7016</v>
+        <v>11.011</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.21</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3689</v>
+        <v>0.3925</v>
       </c>
       <c r="J58" t="n">
-        <v>9.5914</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2276</v>
+        <v>0.2684</v>
       </c>
       <c r="J59" t="n">
-        <v>5.9176</v>
+        <v>6.9784</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.08</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1463</v>
+        <v>0.1908</v>
       </c>
       <c r="J60" t="n">
-        <v>3.8038</v>
+        <v>4.9608</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4422</v>
+        <v>-0.278</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.4972</v>
+        <v>-7.228</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.69</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5747</v>
+        <v>1.0998</v>
       </c>
       <c r="J62" t="n">
-        <v>40.9422</v>
+        <v>28.5948</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.29</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7548</v>
+        <v>0.5878</v>
       </c>
       <c r="J63" t="n">
-        <v>19.6248</v>
+        <v>15.2828</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6267</v>
+        <v>0.5201</v>
       </c>
       <c r="J64" t="n">
-        <v>16.2942</v>
+        <v>13.5226</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1312</v>
+        <v>-0.0541</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.4112</v>
+        <v>-1.4066</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5097</v>
+        <v>-0.4376</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.2522</v>
+        <v>-11.3776</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.01</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1035</v>
+        <v>0.0723</v>
       </c>
       <c r="J67" t="n">
-        <v>2.691</v>
+        <v>1.8798</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0139</v>
+        <v>-0.0347</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.3614</v>
+        <v>-0.9022</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0756</v>
+        <v>-0.0741</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.9656</v>
+        <v>-1.9266</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2342</v>
+        <v>-0.1625</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.0892</v>
+        <v>-4.225</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.53</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7091</v>
+        <v>-0.4777</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.4366</v>
+        <v>-12.4202</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.03</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1364</v>
+        <v>0.1171</v>
       </c>
       <c r="J72" t="n">
-        <v>3.9556</v>
+        <v>3.3959</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.96</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0515</v>
+        <v>-0.0538</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.4935</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1331</v>
+        <v>-0.1024</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.8599</v>
+        <v>-2.9696</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.9455</v>
+        <v>-4.5095</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4851</v>
+        <v>-0.3144</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.0679</v>
+        <v>-9.117599999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>1.262</v>
+        <v>0.8933</v>
       </c>
       <c r="J77" t="n">
-        <v>36.598</v>
+        <v>25.9057</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.884</v>
+        <v>0.6586</v>
       </c>
       <c r="J78" t="n">
-        <v>25.636</v>
+        <v>19.0994</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.21</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5611</v>
+        <v>0.481</v>
       </c>
       <c r="J79" t="n">
-        <v>16.2719</v>
+        <v>13.949</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4341</v>
+        <v>0.4246</v>
       </c>
       <c r="J80" t="n">
-        <v>12.5889</v>
+        <v>12.3134</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8226</v>
+        <v>-0.7768</v>
       </c>
       <c r="J81" t="n">
-        <v>-23.8554</v>
+        <v>-22.5272</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.96</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0111</v>
+        <v>-0.026</v>
       </c>
       <c r="J82" t="n">
-        <v>0.2664</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2193</v>
+        <v>-0.1798</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.2632</v>
+        <v>-4.3152</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.77</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3221</v>
+        <v>-0.2396</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.7304</v>
+        <v>-5.7504</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.66</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5115</v>
+        <v>-0.3419</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.276</v>
+        <v>-8.2056</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.4355</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.5688</v>
+        <v>-10.452</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1308</v>
+        <v>0.8206</v>
       </c>
       <c r="J87" t="n">
-        <v>27.1392</v>
+        <v>19.6944</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.38</v>
       </c>
       <c r="I88" t="n">
-        <v>0.916</v>
+        <v>0.6944</v>
       </c>
       <c r="J88" t="n">
-        <v>21.984</v>
+        <v>16.6656</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.71</v>
+        <v>0.5924</v>
       </c>
       <c r="J89" t="n">
-        <v>17.04</v>
+        <v>14.2176</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.25</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5789</v>
+        <v>0.5262</v>
       </c>
       <c r="J90" t="n">
-        <v>13.8936</v>
+        <v>12.6288</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2208</v>
+        <v>0.306</v>
       </c>
       <c r="J91" t="n">
-        <v>5.2992</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7526</v>
+        <v>0.7295</v>
       </c>
       <c r="J92" t="n">
-        <v>25.5884</v>
+        <v>24.803</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.345</v>
+        <v>0.3492</v>
       </c>
       <c r="J93" t="n">
-        <v>11.73</v>
+        <v>11.8728</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2678</v>
+        <v>0.2952</v>
       </c>
       <c r="J94" t="n">
-        <v>9.1052</v>
+        <v>10.0368</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.167</v>
+        <v>0.2071</v>
       </c>
       <c r="J95" t="n">
-        <v>5.678</v>
+        <v>7.0414</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0818</v>
+        <v>-0.0239</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.7812</v>
+        <v>-0.8126</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.07</v>
       </c>
       <c r="I97" t="n">
-        <v>0.176</v>
+        <v>0.1845</v>
       </c>
       <c r="J97" t="n">
-        <v>5.984</v>
+        <v>6.273</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.04</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1164</v>
+        <v>0.1168</v>
       </c>
       <c r="J98" t="n">
-        <v>3.9576</v>
+        <v>3.9712</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.043</v>
+        <v>0.0383</v>
       </c>
       <c r="J99" t="n">
-        <v>1.462</v>
+        <v>1.3022</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1537</v>
+        <v>-0.0877</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.2258</v>
+        <v>-2.9818</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1913</v>
+        <v>-0.1112</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.5042</v>
+        <v>-3.7808</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.6</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3896</v>
+        <v>1.2531</v>
       </c>
       <c r="J102" t="n">
-        <v>37.5192</v>
+        <v>33.8337</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0706</v>
+        <v>1.0517</v>
       </c>
       <c r="J103" t="n">
-        <v>28.9062</v>
+        <v>28.3959</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5041</v>
+        <v>0.5745</v>
       </c>
       <c r="J104" t="n">
-        <v>13.6107</v>
+        <v>15.5115</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0611</v>
+        <v>0.1382</v>
       </c>
       <c r="J105" t="n">
-        <v>1.6497</v>
+        <v>3.7314</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2012</v>
+        <v>-0.1178</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.4324</v>
+        <v>-3.1806</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.06</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2178</v>
+        <v>0.2106</v>
       </c>
       <c r="J107" t="n">
-        <v>5.8806</v>
+        <v>5.6862</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1359</v>
+        <v>0.1089</v>
       </c>
       <c r="J108" t="n">
-        <v>3.6693</v>
+        <v>2.9403</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2161</v>
+        <v>-0.1611</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.8347</v>
+        <v>-4.3497</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.74</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4267</v>
+        <v>-0.2784</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.5209</v>
+        <v>-7.5168</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6936</v>
+        <v>-0.4663</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.7272</v>
+        <v>-12.5901</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.93</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0449</v>
+        <v>0.0016</v>
       </c>
       <c r="J112" t="n">
-        <v>0.7633</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1088</v>
+        <v>-0.1149</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.8496</v>
+        <v>-1.9533</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.48</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.6968</v>
+        <v>-0.4791</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.8456</v>
+        <v>-8.1447</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.35</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.8728</v>
+        <v>-0.6037</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.8376</v>
+        <v>-10.2629</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.28</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9609</v>
+        <v>-0.6718</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.3353</v>
+        <v>-11.4206</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.57</v>
       </c>
       <c r="I117" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J117" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.5394</v>
+        <v>1.3789</v>
       </c>
       <c r="J118" t="n">
-        <v>26.1698</v>
+        <v>23.4413</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.31</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6046</v>
+        <v>0.7398</v>
       </c>
       <c r="J119" t="n">
-        <v>10.2782</v>
+        <v>12.5766</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3851</v>
+        <v>0.5048</v>
       </c>
       <c r="J120" t="n">
-        <v>6.5467</v>
+        <v>8.5816</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.14</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2196</v>
+        <v>0.3267</v>
       </c>
       <c r="J121" t="n">
-        <v>3.7332</v>
+        <v>5.5539</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4812</v>
+        <v>0.4218</v>
       </c>
       <c r="J122" t="n">
-        <v>13.9548</v>
+        <v>12.2322</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.27</v>
       </c>
       <c r="I123" t="n">
-        <v>0.413</v>
+        <v>0.3639</v>
       </c>
       <c r="J123" t="n">
-        <v>11.977</v>
+        <v>10.5531</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.413</v>
+        <v>0.3639</v>
       </c>
       <c r="J124" t="n">
-        <v>11.977</v>
+        <v>10.5531</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2165</v>
+        <v>0.2196</v>
       </c>
       <c r="J125" t="n">
-        <v>6.2785</v>
+        <v>6.3684</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0713</v>
+        <v>-0.0189</v>
       </c>
       <c r="J126" t="n">
-        <v>-2.0677</v>
+        <v>-0.5481</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4063</v>
+        <v>0.3532</v>
       </c>
       <c r="J127" t="n">
-        <v>11.7827</v>
+        <v>10.2428</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3919</v>
+        <v>0.3388</v>
       </c>
       <c r="J128" t="n">
-        <v>11.3651</v>
+        <v>9.825200000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.1528</v>
+        <v>-2.726</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3818</v>
+        <v>-0.2413</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.0722</v>
+        <v>-6.9977</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6726</v>
+        <v>-0.4498</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.5054</v>
+        <v>-13.0442</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3412</v>
+        <v>0.3748</v>
       </c>
       <c r="J132" t="n">
-        <v>7.8476</v>
+        <v>8.6204</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0128</v>
+        <v>-0.0118</v>
       </c>
       <c r="J133" t="n">
-        <v>0.2944</v>
+        <v>-0.2714</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1211</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.7853</v>
+        <v>-2.1229</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3597</v>
+        <v>-0.2284</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.273099999999999</v>
+        <v>-5.2532</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.3352</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.8588</v>
+        <v>-7.7096</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.56</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2807</v>
+        <v>1.1891</v>
       </c>
       <c r="J137" t="n">
-        <v>29.4561</v>
+        <v>27.3493</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.45</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0571</v>
+        <v>1.0528</v>
       </c>
       <c r="J138" t="n">
-        <v>24.3133</v>
+        <v>24.2144</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.39</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9258</v>
+        <v>0.9584</v>
       </c>
       <c r="J139" t="n">
-        <v>21.2934</v>
+        <v>22.0432</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2667</v>
+        <v>0.356</v>
       </c>
       <c r="J140" t="n">
-        <v>6.1341</v>
+        <v>8.188000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1858</v>
+        <v>0.2731</v>
       </c>
       <c r="J141" t="n">
-        <v>4.2734</v>
+        <v>6.2813</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.32</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5441</v>
+        <v>0.4624</v>
       </c>
       <c r="J142" t="n">
-        <v>16.323</v>
+        <v>13.872</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.17</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3374</v>
+        <v>0.2714</v>
       </c>
       <c r="J143" t="n">
-        <v>10.122</v>
+        <v>8.141999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.095</v>
+        <v>-0.0506</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.85</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3259</v>
+        <v>-0.199</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.776999999999999</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4818</v>
+        <v>-0.3083</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.454</v>
+        <v>-9.249000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>1.041</v>
+        <v>1.0136</v>
       </c>
       <c r="J147" t="n">
-        <v>31.23</v>
+        <v>30.408</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5555</v>
       </c>
       <c r="J148" t="n">
-        <v>17.706</v>
+        <v>16.665</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4074</v>
+        <v>0.3818</v>
       </c>
       <c r="J149" t="n">
-        <v>12.222</v>
+        <v>11.454</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4699</v>
+        <v>-0.2969</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.097</v>
+        <v>-8.907</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.66</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5956</v>
+        <v>-0.3909</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.868</v>
+        <v>-11.727</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.87</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1194</v>
+        <v>-0.1199</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.388</v>
+        <v>-2.398</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.136</v>
+        <v>-0.1315</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.72</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.65</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4953</v>
+        <v>-0.3409</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.906000000000001</v>
+        <v>-6.818</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.628</v>
+        <v>-0.4246</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.56</v>
+        <v>-8.492000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7087</v>
+        <v>-0.4808</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.174</v>
+        <v>-9.616</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.68</v>
       </c>
       <c r="I157" t="n">
-        <v>1.463</v>
+        <v>1.3134</v>
       </c>
       <c r="J157" t="n">
-        <v>29.26</v>
+        <v>26.268</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.3303</v>
+        <v>1.2311</v>
       </c>
       <c r="J158" t="n">
-        <v>26.606</v>
+        <v>24.622</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0649</v>
+        <v>1.0764</v>
       </c>
       <c r="J159" t="n">
-        <v>21.298</v>
+        <v>21.528</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.24</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5004</v>
+        <v>0.6108</v>
       </c>
       <c r="J160" t="n">
-        <v>10.008</v>
+        <v>12.216</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.14</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2598</v>
+        <v>0.36</v>
       </c>
       <c r="J161" t="n">
-        <v>5.196</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.17</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3684</v>
+        <v>0.4107</v>
       </c>
       <c r="J162" t="n">
-        <v>9.210000000000001</v>
+        <v>10.2675</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3382</v>
+        <v>0.3716</v>
       </c>
       <c r="J163" t="n">
-        <v>8.455</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0092</v>
+        <v>-0.0129</v>
       </c>
       <c r="J164" t="n">
-        <v>0.23</v>
+        <v>-0.3225</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.73</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4631</v>
+        <v>-0.298</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.5775</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6823</v>
+        <v>-0.4571</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.0575</v>
+        <v>-11.4275</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9371</v>
+        <v>0.92</v>
       </c>
       <c r="J167" t="n">
-        <v>23.4275</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.07</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2022</v>
+        <v>0.2378</v>
       </c>
       <c r="J168" t="n">
-        <v>5.055</v>
+        <v>5.945</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.134</v>
+        <v>0.1762</v>
       </c>
       <c r="J169" t="n">
-        <v>3.35</v>
+        <v>4.405</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.03</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0617</v>
+        <v>0.109</v>
       </c>
       <c r="J170" t="n">
-        <v>1.5425</v>
+        <v>2.725</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.02</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0225</v>
+        <v>0.0721</v>
       </c>
       <c r="J171" t="n">
-        <v>0.5625</v>
+        <v>1.8025</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9957</v>
+        <v>0.9699</v>
       </c>
       <c r="J172" t="n">
-        <v>29.871</v>
+        <v>29.097</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2408</v>
+        <v>0.2195</v>
       </c>
       <c r="J173" t="n">
-        <v>7.224</v>
+        <v>6.585</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0225</v>
+        <v>0.0473</v>
       </c>
       <c r="J174" t="n">
-        <v>0.675</v>
+        <v>1.419</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2234</v>
+        <v>-0.1736</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.702</v>
+        <v>-5.208</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6813</v>
+        <v>-0.6318</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.439</v>
+        <v>-18.954</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.37</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6071</v>
+        <v>0.7347</v>
       </c>
       <c r="J177" t="n">
-        <v>18.213</v>
+        <v>22.041</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1526</v>
+        <v>0.1605</v>
       </c>
       <c r="J178" t="n">
-        <v>4.578</v>
+        <v>4.815</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1948</v>
+        <v>-0.1123</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.844</v>
+        <v>-3.369</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2951</v>
+        <v>-0.1782</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.853</v>
+        <v>-5.346</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3559</v>
+        <v>-0.2195</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.677</v>
+        <v>-6.585</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4247</v>
+        <v>1.2762</v>
       </c>
       <c r="J182" t="n">
-        <v>37.0422</v>
+        <v>33.1812</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5527</v>
+        <v>0.6209</v>
       </c>
       <c r="J183" t="n">
-        <v>14.3702</v>
+        <v>16.1434</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.21</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5733</v>
       </c>
       <c r="J184" t="n">
-        <v>13.013</v>
+        <v>14.9058</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4745</v>
+        <v>0.5491</v>
       </c>
       <c r="J185" t="n">
-        <v>12.337</v>
+        <v>14.2766</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="J186" t="n">
-        <v>2.353</v>
+        <v>4.3836</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3004</v>
+        <v>0.3173</v>
       </c>
       <c r="J187" t="n">
-        <v>7.8104</v>
+        <v>8.2498</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0375</v>
+        <v>-0.0023</v>
       </c>
       <c r="J188" t="n">
-        <v>0.975</v>
+        <v>-0.0598</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.86</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2236</v>
+        <v>-0.162</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.8136</v>
+        <v>-4.212</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.66</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.356</v>
       </c>
       <c r="J190" t="n">
-        <v>-14.0868</v>
+        <v>-9.256</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.65</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5551</v>
+        <v>-0.3654</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.4326</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.94</v>
       </c>
       <c r="I192" t="n">
-        <v>1.9383</v>
+        <v>1.6357</v>
       </c>
       <c r="J192" t="n">
-        <v>44.5809</v>
+        <v>37.6211</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.47</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0911</v>
+        <v>1.0757</v>
       </c>
       <c r="J193" t="n">
-        <v>25.0953</v>
+        <v>24.7411</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.29</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6556</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>15.0788</v>
+        <v>17.1235</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.1</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1806</v>
+        <v>0.2695</v>
       </c>
       <c r="J195" t="n">
-        <v>4.1538</v>
+        <v>6.1985</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4852</v>
+        <v>-0.4072</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.1596</v>
+        <v>-9.365600000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1509</v>
+        <v>0.1294</v>
       </c>
       <c r="J197" t="n">
-        <v>3.4707</v>
+        <v>2.9762</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.98</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0089</v>
+        <v>-0.02</v>
       </c>
       <c r="J198" t="n">
-        <v>0.2047</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.93</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.095</v>
+        <v>-0.0863</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.185</v>
+        <v>-1.9849</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.75</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.418</v>
+        <v>-0.2711</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.614000000000001</v>
+        <v>-6.2353</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.3946</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.7149</v>
+        <v>-9.075799999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4133</v>
+        <v>1.2679</v>
       </c>
       <c r="J202" t="n">
-        <v>35.3325</v>
+        <v>31.6975</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.25</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6286</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>15.715</v>
+        <v>16.7225</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4839</v>
+        <v>0.5523</v>
       </c>
       <c r="J204" t="n">
-        <v>12.0975</v>
+        <v>13.8075</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3783</v>
+        <v>0.4525</v>
       </c>
       <c r="J205" t="n">
-        <v>9.4575</v>
+        <v>11.3125</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.02</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0402</v>
+        <v>0.0355</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.005</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.378</v>
+        <v>0.4215</v>
       </c>
       <c r="J207" t="n">
-        <v>9.449999999999999</v>
+        <v>10.5375</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3169</v>
+        <v>0.3418</v>
       </c>
       <c r="J208" t="n">
-        <v>7.9225</v>
+        <v>8.545</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2554</v>
+        <v>-0.1654</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.385</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3988</v>
+        <v>-0.2558</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.395</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.54</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7023</v>
+        <v>-0.4724</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.5575</v>
+        <v>-11.81</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.28</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7748</v>
+        <v>0.7624</v>
       </c>
       <c r="J212" t="n">
-        <v>20.1448</v>
+        <v>19.8224</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.21</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6016</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>15.6416</v>
+        <v>15.4518</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3892</v>
+        <v>0.4211</v>
       </c>
       <c r="J214" t="n">
-        <v>10.1192</v>
+        <v>10.9486</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1726</v>
+        <v>0.2274</v>
       </c>
       <c r="J215" t="n">
-        <v>4.4876</v>
+        <v>5.9124</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.04</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0733</v>
+        <v>0.1322</v>
       </c>
       <c r="J216" t="n">
-        <v>1.9058</v>
+        <v>3.4372</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.49</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7851</v>
+        <v>0.9807</v>
       </c>
       <c r="J217" t="n">
-        <v>20.4126</v>
+        <v>25.4982</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.95</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0774</v>
+        <v>-0.0679</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.0124</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.86</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2619</v>
+        <v>-0.1669</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.8094</v>
+        <v>-4.3394</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.73</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.46</v>
+        <v>-0.2965</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.96</v>
+        <v>-7.709</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.51</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.5013</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.2504</v>
+        <v>-13.0338</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.02</v>
       </c>
       <c r="I222" t="n">
-        <v>0.108</v>
+        <v>0.0658</v>
       </c>
       <c r="J222" t="n">
-        <v>2.376</v>
+        <v>1.4476</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.98</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0129</v>
+        <v>-0.0277</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.2838</v>
+        <v>-0.6094000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0129</v>
+        <v>-0.0277</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.2838</v>
+        <v>-0.6094000000000001</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2637</v>
+        <v>-0.1673</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.8014</v>
+        <v>-3.6806</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4749</v>
+        <v>-0.3066</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.4478</v>
+        <v>-6.7452</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.57</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7671</v>
+        <v>0.6884</v>
       </c>
       <c r="J227" t="n">
-        <v>16.8762</v>
+        <v>15.1448</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.31</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4507</v>
+        <v>0.404</v>
       </c>
       <c r="J228" t="n">
-        <v>9.9154</v>
+        <v>8.888</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.201</v>
+        <v>0.2141</v>
       </c>
       <c r="J229" t="n">
-        <v>4.422</v>
+        <v>4.7102</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.14</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1856</v>
+        <v>0.2009</v>
       </c>
       <c r="J230" t="n">
-        <v>4.0832</v>
+        <v>4.4198</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.09</v>
       </c>
       <c r="I231" t="n">
-        <v>0.106</v>
+        <v>0.1316</v>
       </c>
       <c r="J231" t="n">
-        <v>2.332</v>
+        <v>2.8952</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0938</v>
+        <v>1.0613</v>
       </c>
       <c r="J232" t="n">
-        <v>31.7202</v>
+        <v>30.7777</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5423</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>15.7267</v>
+        <v>16.8838</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.18</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4536</v>
+        <v>0.5103</v>
       </c>
       <c r="J234" t="n">
-        <v>13.1544</v>
+        <v>14.7987</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.18</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4536</v>
+        <v>0.5103</v>
       </c>
       <c r="J235" t="n">
-        <v>13.1544</v>
+        <v>14.7987</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0785</v>
+        <v>0.1494</v>
       </c>
       <c r="J236" t="n">
-        <v>2.2765</v>
+        <v>4.3326</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.12</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2927</v>
+        <v>0.3129</v>
       </c>
       <c r="J237" t="n">
-        <v>8.488300000000001</v>
+        <v>9.0741</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.08</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2255</v>
+        <v>0.2287</v>
       </c>
       <c r="J238" t="n">
-        <v>6.5395</v>
+        <v>6.6323</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1928</v>
+        <v>-0.1255</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.5912</v>
+        <v>-3.6395</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4054</v>
+        <v>-0.2586</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.7566</v>
+        <v>-7.4994</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4895</v>
+        <v>-0.3167</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.1955</v>
+        <v>-9.1843</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4919</v>
+        <v>0.4155</v>
       </c>
       <c r="J242" t="n">
-        <v>17.7084</v>
+        <v>14.958</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2093</v>
+        <v>0.1682</v>
       </c>
       <c r="J243" t="n">
-        <v>7.5348</v>
+        <v>6.0552</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0083</v>
+        <v>0.0227</v>
       </c>
       <c r="J244" t="n">
-        <v>0.2988</v>
+        <v>0.8172</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.93</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1892</v>
+        <v>-0.1049</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.8112</v>
+        <v>-3.7764</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2412</v>
+        <v>-0.1393</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.683199999999999</v>
+        <v>-5.0148</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4455</v>
+        <v>0.4069</v>
       </c>
       <c r="J247" t="n">
-        <v>16.038</v>
+        <v>14.6484</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4041</v>
+        <v>0.3676</v>
       </c>
       <c r="J248" t="n">
-        <v>14.5476</v>
+        <v>13.2336</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.05</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0755</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>2.718</v>
+        <v>3.4092</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.03</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0341</v>
+        <v>0.0584</v>
       </c>
       <c r="J250" t="n">
-        <v>1.2276</v>
+        <v>2.1024</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.187</v>
+        <v>-0.0993</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.732</v>
+        <v>-3.5748</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.18</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3928</v>
+        <v>0.441</v>
       </c>
       <c r="J252" t="n">
-        <v>9.427199999999999</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1788</v>
+        <v>0.1679</v>
       </c>
       <c r="J253" t="n">
-        <v>4.2912</v>
+        <v>4.0296</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.92</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1307</v>
+        <v>-0.102</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.1368</v>
+        <v>-2.448</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.72</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4703</v>
+        <v>-0.3043</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.2872</v>
+        <v>-7.3032</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6283</v>
+        <v>-0.4173</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.0792</v>
+        <v>-10.0152</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.72</v>
       </c>
       <c r="I257" t="n">
-        <v>1.605</v>
+        <v>1.3954</v>
       </c>
       <c r="J257" t="n">
-        <v>38.52</v>
+        <v>33.4896</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.37</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9106</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J258" t="n">
-        <v>21.8544</v>
+        <v>22.3176</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.17</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3919</v>
+        <v>0.4723</v>
       </c>
       <c r="J259" t="n">
-        <v>9.4056</v>
+        <v>11.3352</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1759</v>
+        <v>0.2564</v>
       </c>
       <c r="J260" t="n">
-        <v>4.2216</v>
+        <v>6.1536</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.02</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.0487</v>
+        <v>0.0293</v>
       </c>
       <c r="J261" t="n">
-        <v>-1.1688</v>
+        <v>0.7032</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.27</v>
       </c>
       <c r="I262" t="n">
-        <v>0.5206</v>
+        <v>0.6135</v>
       </c>
       <c r="J262" t="n">
-        <v>13.5356</v>
+        <v>15.951</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1179</v>
+        <v>0.0934</v>
       </c>
       <c r="J263" t="n">
-        <v>3.0654</v>
+        <v>2.4284</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.98</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0023</v>
+        <v>-0.0243</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.0598</v>
+        <v>-0.6318</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.7</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4963</v>
+        <v>-0.3226</v>
       </c>
       <c r="J265" t="n">
-        <v>-12.9038</v>
+        <v>-8.387600000000001</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.47</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7846</v>
+        <v>-0.5352</v>
       </c>
       <c r="J266" t="n">
-        <v>-20.3996</v>
+        <v>-13.9152</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.52</v>
       </c>
       <c r="I267" t="n">
-        <v>1.231</v>
+        <v>1.1522</v>
       </c>
       <c r="J267" t="n">
-        <v>32.006</v>
+        <v>29.9572</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9604</v>
+        <v>0.9715</v>
       </c>
       <c r="J268" t="n">
-        <v>24.9704</v>
+        <v>25.259</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.26</v>
       </c>
       <c r="I269" t="n">
-        <v>0.636</v>
+        <v>0.6896</v>
       </c>
       <c r="J269" t="n">
-        <v>16.536</v>
+        <v>17.9296</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.09</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1797</v>
+        <v>0.2588</v>
       </c>
       <c r="J270" t="n">
-        <v>4.6722</v>
+        <v>6.7288</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.06</v>
       </c>
       <c r="I271" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="J271" t="n">
-        <v>2.353</v>
+        <v>4.3836</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.85</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7918</v>
+        <v>1.5235</v>
       </c>
       <c r="J272" t="n">
-        <v>39.4196</v>
+        <v>33.517</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.52</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1793</v>
+        <v>1.1324</v>
       </c>
       <c r="J273" t="n">
-        <v>25.9446</v>
+        <v>24.9128</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.3</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6633</v>
+        <v>0.7614</v>
       </c>
       <c r="J274" t="n">
-        <v>14.5926</v>
+        <v>16.7508</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.17</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3529</v>
+        <v>0.4507</v>
       </c>
       <c r="J275" t="n">
-        <v>7.7638</v>
+        <v>9.9154</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0766</v>
+        <v>0.007</v>
       </c>
       <c r="J276" t="n">
-        <v>-1.6852</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.03</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2009</v>
+        <v>0.1846</v>
       </c>
       <c r="J277" t="n">
-        <v>4.4198</v>
+        <v>4.0612</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.77</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.3137</v>
+        <v>-0.2382</v>
       </c>
       <c r="J278" t="n">
-        <v>-6.9014</v>
+        <v>-5.2404</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.72</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4128</v>
+        <v>-0.284</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.0816</v>
+        <v>-6.248</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.67</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4919</v>
+        <v>-0.3307</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.8218</v>
+        <v>-7.2754</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.53</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6846</v>
+        <v>-0.4617</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.0612</v>
+        <v>-10.1574</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.58</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3086</v>
+        <v>1.209</v>
       </c>
       <c r="J282" t="n">
-        <v>27.4806</v>
+        <v>25.389</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.53</v>
       </c>
       <c r="I283" t="n">
-        <v>1.21</v>
+        <v>1.1481</v>
       </c>
       <c r="J283" t="n">
-        <v>25.41</v>
+        <v>24.1101</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.35</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8061</v>
+        <v>0.8736</v>
       </c>
       <c r="J284" t="n">
-        <v>16.9281</v>
+        <v>18.3456</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.17</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3606</v>
+        <v>0.4555</v>
       </c>
       <c r="J285" t="n">
-        <v>7.5726</v>
+        <v>9.5655</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.12</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2321</v>
+        <v>0.3234</v>
       </c>
       <c r="J286" t="n">
-        <v>4.8741</v>
+        <v>6.7914</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.95</v>
       </c>
       <c r="I287" t="n">
-        <v>0.0123</v>
+        <v>-0.0267</v>
       </c>
       <c r="J287" t="n">
-        <v>0.2583</v>
+        <v>-0.5607</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.196</v>
+        <v>-0.1704</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.116</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.73</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3606</v>
+        <v>-0.2715</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.5726</v>
+        <v>-5.7015</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.6354</v>
+        <v>-0.4283</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.3434</v>
+        <v>-8.994300000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7403</v>
+        <v>-0.503</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.5463</v>
+        <v>-10.563</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4933</v>
+        <v>1.3172</v>
       </c>
       <c r="J292" t="n">
-        <v>43.3057</v>
+        <v>38.1988</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.39</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0339</v>
+        <v>1.0106</v>
       </c>
       <c r="J293" t="n">
-        <v>29.9831</v>
+        <v>29.3074</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3901</v>
+        <v>0.3986</v>
       </c>
       <c r="J294" t="n">
-        <v>11.3129</v>
+        <v>11.5594</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.84</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.611</v>
+        <v>-0.5507</v>
       </c>
       <c r="J295" t="n">
-        <v>-17.719</v>
+        <v>-15.9703</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.64</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.0677</v>
+        <v>-1.0513</v>
       </c>
       <c r="J296" t="n">
-        <v>-30.9633</v>
+        <v>-30.4877</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.26</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4498</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>13.0442</v>
+        <v>15.3613</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.24</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4223</v>
+        <v>0.4947</v>
       </c>
       <c r="J298" t="n">
-        <v>12.2467</v>
+        <v>14.3463</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.11</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2242</v>
+        <v>0.2548</v>
       </c>
       <c r="J299" t="n">
-        <v>6.5018</v>
+        <v>7.3892</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.87</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2911</v>
+        <v>-0.1727</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.4419</v>
+        <v>-5.0083</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4228</v>
+        <v>-0.2648</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.2612</v>
+        <v>-7.6792</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0453</v>
+        <v>0.0121</v>
       </c>
       <c r="J302" t="n">
-        <v>1.2231</v>
+        <v>0.3267</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0101</v>
+        <v>-0.0126</v>
       </c>
       <c r="J303" t="n">
-        <v>0.2727</v>
+        <v>-0.3402</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.96</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0612</v>
+        <v>-0.0563</v>
       </c>
       <c r="J304" t="n">
-        <v>-1.6524</v>
+        <v>-1.5201</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.91</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1735</v>
+        <v>-0.1148</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.6845</v>
+        <v>-3.0996</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4626</v>
+        <v>-0.2977</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.4902</v>
+        <v>-8.0379</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.75</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9747</v>
+        <v>0.8915</v>
       </c>
       <c r="J307" t="n">
-        <v>26.3169</v>
+        <v>24.0705</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.29</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4429</v>
+        <v>0.388</v>
       </c>
       <c r="J308" t="n">
-        <v>11.9583</v>
+        <v>10.476</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.11</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1535</v>
+        <v>0.1666</v>
       </c>
       <c r="J309" t="n">
-        <v>4.1445</v>
+        <v>4.4982</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="J310" t="n">
-        <v>-1.89</v>
+        <v>-0.4941</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.83</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3774</v>
+        <v>-0.2292</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.1898</v>
+        <v>-6.1884</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.33</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9404</v>
+        <v>0.9173</v>
       </c>
       <c r="J312" t="n">
-        <v>27.2716</v>
+        <v>26.6017</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.22</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6837</v>
+        <v>0.6488</v>
       </c>
       <c r="J313" t="n">
-        <v>19.8273</v>
+        <v>18.8152</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.16</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5291</v>
+        <v>0.4945</v>
       </c>
       <c r="J314" t="n">
-        <v>15.3439</v>
+        <v>14.3405</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.96</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2348</v>
+        <v>-0.179</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.8092</v>
+        <v>-5.191</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.1159</v>
+        <v>-1.1062</v>
       </c>
       <c r="J316" t="n">
-        <v>-32.3611</v>
+        <v>-32.0798</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3551</v>
+        <v>0.4023</v>
       </c>
       <c r="J317" t="n">
-        <v>10.2979</v>
+        <v>11.6667</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2113</v>
+        <v>0.2263</v>
       </c>
       <c r="J318" t="n">
-        <v>6.1277</v>
+        <v>6.5627</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1346</v>
+        <v>-0.0757</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.9034</v>
+        <v>-2.1953</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.93</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1736</v>
+        <v>-0.0998</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.0344</v>
+        <v>-2.8942</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.84</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3239</v>
+        <v>-0.1981</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.3931</v>
+        <v>-5.7449</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.16</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3519</v>
+        <v>0.3897</v>
       </c>
       <c r="J322" t="n">
-        <v>9.501300000000001</v>
+        <v>10.5219</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.96</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.057</v>
       </c>
       <c r="J323" t="n">
-        <v>-1.7334</v>
+        <v>-1.539</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1074</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J324" t="n">
-        <v>-2.8998</v>
+        <v>-2.2059</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3173</v>
+        <v>-0.1996</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.5671</v>
+        <v>-5.3892</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.73</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4641</v>
+        <v>-0.2985</v>
       </c>
       <c r="J326" t="n">
-        <v>-12.5307</v>
+        <v>-8.0595</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.56</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3297</v>
+        <v>1.2121</v>
       </c>
       <c r="J327" t="n">
-        <v>35.9019</v>
+        <v>32.7267</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.35</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8944</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="J328" t="n">
-        <v>24.1488</v>
+        <v>24.3189</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.07</v>
       </c>
       <c r="I329" t="n">
-        <v>0.1373</v>
+        <v>0.2096</v>
       </c>
       <c r="J329" t="n">
-        <v>3.7071</v>
+        <v>5.6592</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.07</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1373</v>
+        <v>0.2096</v>
       </c>
       <c r="J330" t="n">
-        <v>3.7071</v>
+        <v>5.6592</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.06</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1064</v>
+        <v>0.1788</v>
       </c>
       <c r="J331" t="n">
-        <v>2.8728</v>
+        <v>4.8276</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.34</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5577</v>
+        <v>0.6701</v>
       </c>
       <c r="J332" t="n">
-        <v>22.8657</v>
+        <v>27.4741</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2937</v>
+        <v>0.3339</v>
       </c>
       <c r="J333" t="n">
-        <v>12.0417</v>
+        <v>13.6899</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.91</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2232</v>
+        <v>-0.1277</v>
       </c>
       <c r="J334" t="n">
-        <v>-9.151199999999999</v>
+        <v>-5.2357</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.91</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2232</v>
+        <v>-0.1277</v>
       </c>
       <c r="J335" t="n">
-        <v>-9.151199999999999</v>
+        <v>-5.2357</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.9</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2401</v>
+        <v>-0.1389</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.844099999999999</v>
+        <v>-5.6949</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.18</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5921</v>
+        <v>0.5525</v>
       </c>
       <c r="J337" t="n">
-        <v>24.2761</v>
+        <v>22.6525</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5393</v>
+        <v>0.5</v>
       </c>
       <c r="J338" t="n">
-        <v>22.1113</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.16</v>
       </c>
       <c r="I339" t="n">
-        <v>0.5393</v>
+        <v>0.5</v>
       </c>
       <c r="J339" t="n">
-        <v>22.1113</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3262</v>
+        <v>-0.271</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.3742</v>
+        <v>-11.111</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.77</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="J341" t="n">
-        <v>-30.9755</v>
+        <v>-29.1182</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5435/event_5435_evp_summary.xlsx
+++ b/database/event/5435/event_5435_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2216</v>
+        <v>6.1917</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2372</v>
+        <v>1.2312</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1707</v>
+        <v>2.1944</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2216</v>
+        <v>6.1917</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9367</v>
+        <v>3.9043</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2849</v>
+        <v>2.2874</v>
       </c>
       <c r="H2" t="n">
-        <v>8.3842</v>
+        <v>7.9877</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3594</v>
+        <v>4.3133</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2849</v>
+        <v>2.2874</v>
       </c>
       <c r="K2" t="n">
         <v>91</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.644299999999999</v>
+        <v>6.6007</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2031</v>
+        <v>6.1811</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2335</v>
+        <v>1.2291</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1624</v>
+        <v>2.1896</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2031</v>
+        <v>6.1811</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4042</v>
+        <v>3.3207</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7989</v>
+        <v>2.8604</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5079</v>
+        <v>6.0619</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3838</v>
+        <v>3.2734</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7989</v>
+        <v>2.8604</v>
       </c>
       <c r="K3" t="n">
         <v>91</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>6.182700000000001</v>
+        <v>6.1338</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0185</v>
+        <v>6.116</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1968</v>
+        <v>1.2162</v>
       </c>
       <c r="D4" t="n">
-        <v>2.079</v>
+        <v>2.1599</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0185</v>
+        <v>6.116</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0464</v>
+        <v>2.9547</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9721</v>
+        <v>3.1613</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2474</v>
+        <v>4.8545</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7284</v>
+        <v>2.6214</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9721</v>
+        <v>3.1613</v>
       </c>
       <c r="K4" t="n">
         <v>195</v>
@@ -621,7 +621,7 @@
         <v>191</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7005</v>
+        <v>5.7827</v>
       </c>
       <c r="N4" t="n">
         <v>386</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9173</v>
+        <v>5.7781</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1767</v>
+        <v>1.149</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0334</v>
+        <v>2.0061</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9173</v>
+        <v>5.7781</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7761</v>
+        <v>1.5871</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1412</v>
+        <v>4.191</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7761</v>
+        <v>1.5871</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9235</v>
+        <v>0.857</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1412</v>
+        <v>4.191</v>
       </c>
       <c r="K5" t="n">
         <v>195</v>
@@ -667,7 +667,7 @@
         <v>191</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0647</v>
+        <v>5.048</v>
       </c>
       <c r="N5" t="n">
         <v>386</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5413</v>
+        <v>4.6006</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9031</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4122</v>
+        <v>1.4701</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5413</v>
+        <v>4.6006</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5796</v>
+        <v>2.537</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9617</v>
+        <v>2.0636</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6026</v>
+        <v>3.4762</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8732</v>
+        <v>1.8771</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9617</v>
+        <v>2.0636</v>
       </c>
       <c r="K6" t="n">
         <v>195</v>
@@ -713,7 +713,7 @@
         <v>191</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8349</v>
+        <v>3.9407</v>
       </c>
       <c r="N6" t="n">
         <v>386</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0173</v>
+        <v>4.058</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1756</v>
+        <v>1.2231</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0173</v>
+        <v>4.058</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4851</v>
+        <v>3.4228</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5322</v>
+        <v>0.6352</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7929</v>
+        <v>6.3988</v>
       </c>
       <c r="I7" t="n">
-        <v>3.532</v>
+        <v>3.4553</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5322</v>
+        <v>0.6352</v>
       </c>
       <c r="K7" t="n">
         <v>195</v>
@@ -759,7 +759,7 @@
         <v>191</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0642</v>
+        <v>4.0905</v>
       </c>
       <c r="N7" t="n">
         <v>386</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.952</v>
+        <v>4.0368</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7859</v>
+        <v>0.8027</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1461</v>
+        <v>1.2134</v>
       </c>
       <c r="E8" t="n">
-        <v>3.952</v>
+        <v>4.0368</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9404</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0116</v>
+        <v>1.1568</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8739</v>
+        <v>4.608</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5342</v>
+        <v>2.4883</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0116</v>
+        <v>1.1568</v>
       </c>
       <c r="K8" t="n">
         <v>91</v>
@@ -805,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5458</v>
+        <v>3.6451</v>
       </c>
       <c r="N8" t="n">
         <v>281</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8252</v>
+        <v>3.718</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7607</v>
+        <v>0.7393</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0889</v>
+        <v>1.0683</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8252</v>
+        <v>3.718</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6309</v>
+        <v>3.5285</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1943</v>
+        <v>0.1895</v>
       </c>
       <c r="H9" t="n">
-        <v>7.3066</v>
+        <v>6.7477</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7991</v>
+        <v>3.6437</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1943</v>
+        <v>0.1895</v>
       </c>
       <c r="K9" t="n">
         <v>193</v>
@@ -851,7 +851,7 @@
         <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9934</v>
+        <v>3.8332</v>
       </c>
       <c r="N9" t="n">
         <v>245</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6238</v>
+        <v>3.6217</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7206</v>
+        <v>0.7202</v>
       </c>
       <c r="D10" t="n">
-        <v>0.998</v>
+        <v>1.0245</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6238</v>
+        <v>3.6217</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4095</v>
+        <v>3.3758</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2143</v>
+        <v>0.2459</v>
       </c>
       <c r="H10" t="n">
-        <v>6.5267</v>
+        <v>6.244</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3936</v>
+        <v>3.3717</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2143</v>
+        <v>0.2459</v>
       </c>
       <c r="K10" t="n">
         <v>91</v>
@@ -897,7 +897,7 @@
         <v>190</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6079</v>
+        <v>3.6176</v>
       </c>
       <c r="N10" t="n">
         <v>281</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4152</v>
+        <v>3.5074</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6791</v>
+        <v>0.6975</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9038</v>
+        <v>0.9724</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4152</v>
+        <v>3.5074</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5282</v>
+        <v>2.4686</v>
       </c>
       <c r="G11" t="n">
-        <v>0.887</v>
+        <v>1.0388</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4216</v>
+        <v>3.2506</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7791</v>
+        <v>1.7553</v>
       </c>
       <c r="J11" t="n">
-        <v>0.887</v>
+        <v>1.0388</v>
       </c>
       <c r="K11" t="n">
         <v>195</v>
@@ -943,7 +943,7 @@
         <v>191</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6661</v>
+        <v>2.7941</v>
       </c>
       <c r="N11" t="n">
         <v>386</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.201</v>
+        <v>3.2051</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6365</v>
+        <v>0.6373</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8071</v>
+        <v>0.8348</v>
       </c>
       <c r="E12" t="n">
-        <v>3.201</v>
+        <v>3.2051</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5137</v>
+        <v>3.5405</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3127</v>
+        <v>-0.3354</v>
       </c>
       <c r="H12" t="n">
-        <v>6.8939</v>
+        <v>6.7873</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5845</v>
+        <v>3.6651</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3127</v>
+        <v>-0.3354</v>
       </c>
       <c r="K12" t="n">
         <v>193</v>
@@ -989,7 +989,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2718</v>
+        <v>3.3297</v>
       </c>
       <c r="N12" t="n">
         <v>245</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9717</v>
+        <v>2.9465</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5909</v>
+        <v>0.5859</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7036</v>
+        <v>0.7171</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9717</v>
+        <v>2.9465</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5069</v>
+        <v>2.447</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4648</v>
+        <v>0.4995</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3464</v>
+        <v>3.1795</v>
       </c>
       <c r="I13" t="n">
-        <v>1.74</v>
+        <v>1.7169</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4648</v>
+        <v>0.4995</v>
       </c>
       <c r="K13" t="n">
         <v>193</v>
@@ -1035,7 +1035,7 @@
         <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2048</v>
+        <v>2.2164</v>
       </c>
       <c r="N13" t="n">
         <v>245</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6262</v>
+        <v>2.5813</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5222</v>
+        <v>0.5133</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5476</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6262</v>
+        <v>2.5813</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6804</v>
+        <v>2.5964</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0542</v>
+        <v>-0.0151</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9578</v>
+        <v>3.6723</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0579</v>
+        <v>1.983</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0542</v>
+        <v>-0.0151</v>
       </c>
       <c r="K14" t="n">
         <v>193</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0037</v>
+        <v>1.9679</v>
       </c>
       <c r="N14" t="n">
         <v>245</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5263</v>
+        <v>2.4368</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5024</v>
+        <v>0.4846</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4851</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5263</v>
+        <v>2.4368</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7511</v>
+        <v>2.6775</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2248</v>
+        <v>-0.2407</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2067</v>
+        <v>3.9399</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1873</v>
+        <v>2.1275</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2248</v>
+        <v>-0.2407</v>
       </c>
       <c r="K15" t="n">
         <v>145</v>
@@ -1127,7 +1127,7 @@
         <v>53</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9625</v>
+        <v>1.8868</v>
       </c>
       <c r="N15" t="n">
         <v>198</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3287</v>
+        <v>2.2882</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4631</v>
+        <v>0.455</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4133</v>
+        <v>0.4174</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3287</v>
+        <v>2.2882</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3287</v>
+        <v>2.2882</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3287</v>
+        <v>2.2882</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3287</v>
+        <v>2.2882</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3287</v>
+        <v>2.2882</v>
       </c>
       <c r="N16" t="n">
         <v>222</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3064</v>
+        <v>2.2467</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4586</v>
+        <v>0.4468</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4032</v>
+        <v>0.3985</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3064</v>
+        <v>2.2467</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2781</v>
+        <v>2.2467</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0283</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5402</v>
+        <v>2.2467</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3208</v>
+        <v>2.2467</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0283</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3491</v>
+        <v>2.2467</v>
       </c>
       <c r="N17" t="n">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2643</v>
+        <v>2.2277</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4503</v>
+        <v>0.443</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3842</v>
+        <v>0.3899</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2643</v>
+        <v>2.2277</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8553</v>
+        <v>2.2048</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.591</v>
+        <v>0.0229</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5741</v>
+        <v>2.3804</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3783</v>
+        <v>1.2854</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.591</v>
+        <v>0.0229</v>
       </c>
       <c r="K18" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="L18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7873</v>
+        <v>1.3083</v>
       </c>
       <c r="N18" t="n">
-        <v>198</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2561</v>
+        <v>2.1488</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4486</v>
+        <v>0.4273</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3805</v>
+        <v>0.354</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2561</v>
+        <v>2.1488</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2561</v>
+        <v>2.7684</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6196</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2561</v>
+        <v>4.2397</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2561</v>
+        <v>2.2894</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6196</v>
       </c>
       <c r="K19" t="n">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2561</v>
+        <v>1.6698</v>
       </c>
       <c r="N19" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2205</v>
+        <v>2.117</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4416</v>
+        <v>0.421</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3644</v>
+        <v>0.3395</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2205</v>
+        <v>2.117</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5609</v>
+        <v>2.4894</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3404</v>
+        <v>-0.3724</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5369</v>
+        <v>3.3191</v>
       </c>
       <c r="I20" t="n">
-        <v>1.839</v>
+        <v>1.7923</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3404</v>
+        <v>-0.3724</v>
       </c>
       <c r="K20" t="n">
         <v>145</v>
@@ -1357,7 +1357,7 @@
         <v>53</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4986</v>
+        <v>1.4199</v>
       </c>
       <c r="N20" t="n">
         <v>198</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.923</v>
+        <v>1.8771</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3824</v>
+        <v>0.3733</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2301</v>
+        <v>0.2303</v>
       </c>
       <c r="E21" t="n">
-        <v>1.923</v>
+        <v>1.8771</v>
       </c>
       <c r="F21" t="n">
-        <v>1.923</v>
+        <v>1.8771</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.923</v>
+        <v>1.8771</v>
       </c>
       <c r="I21" t="n">
-        <v>1.923</v>
+        <v>1.8771</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.923</v>
+        <v>1.8771</v>
       </c>
       <c r="N21" t="n">
         <v>222</v>
@@ -1412,78 +1412,78 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6162</v>
+        <v>1.5838</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3214</v>
+        <v>0.3149</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0916</v>
+        <v>0.0968</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6162</v>
+        <v>1.5838</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6162</v>
+        <v>1.5838</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6162</v>
+        <v>1.5838</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6162</v>
+        <v>1.5838</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6162</v>
+        <v>1.5838</v>
       </c>
       <c r="N22" t="n">
-        <v>231</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>s0m</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.611</v>
+        <v>1.5383</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3204</v>
+        <v>0.3059</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0893</v>
+        <v>0.0761</v>
       </c>
       <c r="E23" t="n">
-        <v>1.611</v>
+        <v>1.5383</v>
       </c>
       <c r="F23" t="n">
-        <v>1.611</v>
+        <v>1.5383</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.611</v>
+        <v>1.5383</v>
       </c>
       <c r="I23" t="n">
-        <v>1.611</v>
+        <v>1.5383</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.611</v>
+        <v>1.5383</v>
       </c>
       <c r="N23" t="n">
         <v>141</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>s0m</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5775</v>
+        <v>1.4878</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3137</v>
+        <v>0.2959</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0741</v>
+        <v>0.0531</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5775</v>
+        <v>1.4878</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5775</v>
+        <v>1.4878</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5775</v>
+        <v>1.4878</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5775</v>
+        <v>1.4878</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5775</v>
+        <v>1.4878</v>
       </c>
       <c r="N24" t="n">
-        <v>141</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4056</v>
+        <v>1.2947</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2795</v>
+        <v>0.2575</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0035</v>
+        <v>-0.0348</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4056</v>
+        <v>1.2947</v>
       </c>
       <c r="F25" t="n">
-        <v>1.699</v>
+        <v>1.6193</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2934</v>
+        <v>-0.3246</v>
       </c>
       <c r="H25" t="n">
-        <v>1.699</v>
+        <v>1.6193</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8834</v>
+        <v>0.8744</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2934</v>
+        <v>-0.3246</v>
       </c>
       <c r="K25" t="n">
         <v>145</v>
@@ -1587,7 +1587,7 @@
         <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>0.59</v>
+        <v>0.5498</v>
       </c>
       <c r="N25" t="n">
         <v>198</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3299</v>
+        <v>1.2017</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2645</v>
+        <v>0.239</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0376</v>
+        <v>-0.0772</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3299</v>
+        <v>1.2017</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3299</v>
+        <v>1.2017</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3299</v>
+        <v>1.2017</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3299</v>
+        <v>1.2017</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3299</v>
+        <v>1.2017</v>
       </c>
       <c r="N26" t="n">
         <v>222</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2117</v>
+        <v>1.1142</v>
       </c>
       <c r="C27" t="n">
-        <v>0.241</v>
+        <v>0.2216</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.091</v>
+        <v>-0.117</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2117</v>
+        <v>1.1142</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2117</v>
+        <v>1.1142</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2117</v>
+        <v>1.1142</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2117</v>
+        <v>1.1142</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2117</v>
+        <v>1.1142</v>
       </c>
       <c r="N27" t="n">
         <v>231</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1159</v>
+        <v>1.0324</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2219</v>
+        <v>0.2053</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1342</v>
+        <v>-0.1542</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1159</v>
+        <v>1.0324</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1159</v>
+        <v>1.0324</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1159</v>
+        <v>1.0324</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1159</v>
+        <v>1.0324</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1159</v>
+        <v>1.0324</v>
       </c>
       <c r="N28" t="n">
         <v>231</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8651</v>
+        <v>0.8461</v>
       </c>
       <c r="C29" t="n">
-        <v>0.172</v>
+        <v>0.1683</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2475</v>
+        <v>-0.239</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8651</v>
+        <v>0.8461</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8651</v>
+        <v>0.8461</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8651</v>
+        <v>0.8461</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8651</v>
+        <v>0.8461</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8651</v>
+        <v>0.8461</v>
       </c>
       <c r="N29" t="n">
         <v>231</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6438</v>
+        <v>0.5945</v>
       </c>
       <c r="C30" t="n">
-        <v>0.128</v>
+        <v>0.1182</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3474</v>
+        <v>-0.3536</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6438</v>
+        <v>0.5945</v>
       </c>
       <c r="F30" t="n">
-        <v>0.926</v>
+        <v>0.9111</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2822</v>
+        <v>-0.3166</v>
       </c>
       <c r="H30" t="n">
-        <v>0.926</v>
+        <v>0.9111</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4815</v>
+        <v>0.492</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2822</v>
+        <v>-0.3166</v>
       </c>
       <c r="K30" t="n">
         <v>145</v>
@@ -1817,7 +1817,7 @@
         <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1993</v>
+        <v>0.1754</v>
       </c>
       <c r="N30" t="n">
         <v>198</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2552</v>
+        <v>0.2182</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0507</v>
+        <v>0.0434</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5228</v>
+        <v>-0.5249</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2552</v>
+        <v>0.2182</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2552</v>
+        <v>0.2182</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2552</v>
+        <v>0.2182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2552</v>
+        <v>0.2182</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2552</v>
+        <v>0.2182</v>
       </c>
       <c r="N31" t="n">
         <v>141</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0083</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0017</v>
+        <v>0.0154</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6343</v>
+        <v>-0.589</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0083</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9787</v>
+        <v>1.0219</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.9704</v>
+        <v>-0.9446</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9787</v>
+        <v>1.0219</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5089</v>
+        <v>0.5518</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9704</v>
+        <v>-0.9446</v>
       </c>
       <c r="K32" t="n">
         <v>91</v>
@@ -1909,7 +1909,7 @@
         <v>190</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4615</v>
+        <v>-0.3928</v>
       </c>
       <c r="N32" t="n">
         <v>281</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2598</v>
+        <v>-0.3327</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0517</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7553</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2598</v>
+        <v>-0.3327</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2598</v>
+        <v>-0.3327</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2598</v>
+        <v>-0.3327</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2598</v>
+        <v>-0.3327</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2598</v>
+        <v>-0.3327</v>
       </c>
       <c r="N33" t="n">
         <v>118</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3616</v>
+        <v>-0.3757</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8013</v>
+        <v>-0.7952</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3616</v>
+        <v>-0.3757</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3616</v>
+        <v>-0.3757</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3616</v>
+        <v>-0.3757</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3616</v>
+        <v>-0.3757</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3616</v>
+        <v>-0.3757</v>
       </c>
       <c r="N34" t="n">
         <v>141</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4393</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8156</v>
+        <v>-0.8242</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4393</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4393</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4393</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4393</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3933</v>
+        <v>-0.4393</v>
       </c>
       <c r="N35" t="n">
         <v>118</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6223</v>
+        <v>-0.6963</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1237</v>
+        <v>-0.1385</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.919</v>
+        <v>-0.9412</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6223</v>
+        <v>-0.6963</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6223</v>
+        <v>-0.6963</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6223</v>
+        <v>-0.6963</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6223</v>
+        <v>-0.6963</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6223</v>
+        <v>-0.6963</v>
       </c>
       <c r="N36" t="n">
         <v>118</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7811</v>
+        <v>-0.8438</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1553</v>
+        <v>-0.1678</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9906</v>
+        <v>-1.0083</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7811</v>
+        <v>-0.8438</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7811</v>
+        <v>-0.8438</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7811</v>
+        <v>-0.8438</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7811</v>
+        <v>-0.8438</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7811</v>
+        <v>-0.8438</v>
       </c>
       <c r="N37" t="n">
         <v>118</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9411</v>
+        <v>-1.0074</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1871</v>
+        <v>-0.2003</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0629</v>
+        <v>-1.0828</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9411</v>
+        <v>-1.0074</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9411</v>
+        <v>-1.0074</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9411</v>
+        <v>-1.0074</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9411</v>
+        <v>-1.0074</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9411</v>
+        <v>-1.0074</v>
       </c>
       <c r="N38" t="n">
         <v>222</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.97</v>
+        <v>-1.0284</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1929</v>
+        <v>-0.2045</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0759</v>
+        <v>-1.0924</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.97</v>
+        <v>-1.0284</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.97</v>
+        <v>-1.0284</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.97</v>
+        <v>-1.0284</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.97</v>
+        <v>-1.0284</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.97</v>
+        <v>-1.0284</v>
       </c>
       <c r="N39" t="n">
         <v>141</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7809</v>
+        <v>-1.8541</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3541</v>
+        <v>-0.3687</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.442</v>
+        <v>-1.4682</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7809</v>
+        <v>-1.8541</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7809</v>
+        <v>-1.8541</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7809</v>
+        <v>-1.8541</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7809</v>
+        <v>-1.8541</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7809</v>
+        <v>-1.8541</v>
       </c>
       <c r="N40" t="n">
         <v>118</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.761</v>
+        <v>-2.6193</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.549</v>
+        <v>-0.5209</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8845</v>
+        <v>-1.8166</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.761</v>
+        <v>-2.6193</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.761</v>
+        <v>-2.6193</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.761</v>
+        <v>-2.6193</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.761</v>
+        <v>-2.6193</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.761</v>
+        <v>-2.6193</v>
       </c>
       <c r="N41" t="n">
         <v>231</v>
@@ -2429,10 +2429,10 @@
         <v>1.27</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5617</v>
+        <v>0.5474</v>
       </c>
       <c r="J2" t="n">
-        <v>19.6595</v>
+        <v>19.159</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4906</v>
+        <v>0.4822</v>
       </c>
       <c r="J3" t="n">
-        <v>17.171</v>
+        <v>16.877</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1819</v>
+        <v>0.1903</v>
       </c>
       <c r="J4" t="n">
-        <v>6.3665</v>
+        <v>6.6605</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.157</v>
+        <v>-0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.495</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4392</v>
+        <v>-0.4466</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.372</v>
+        <v>-15.631</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8329</v>
+        <v>0.7845</v>
       </c>
       <c r="J7" t="n">
-        <v>29.1515</v>
+        <v>27.4575</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6187</v>
+        <v>0.5955</v>
       </c>
       <c r="J8" t="n">
-        <v>21.6545</v>
+        <v>20.8425</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J9" t="n">
-        <v>10.0135</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2274</v>
+        <v>0.2373</v>
       </c>
       <c r="J10" t="n">
-        <v>7.959</v>
+        <v>8.3055</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1651</v>
+        <v>0.1784</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7785</v>
+        <v>6.244</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.64</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7631</v>
+        <v>0.7562</v>
       </c>
       <c r="J12" t="n">
-        <v>19.0775</v>
+        <v>18.905</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.505</v>
+        <v>0.5154</v>
       </c>
       <c r="J13" t="n">
-        <v>12.625</v>
+        <v>12.885</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2655</v>
+        <v>0.2841</v>
       </c>
       <c r="J14" t="n">
-        <v>6.6375</v>
+        <v>7.1025</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1022</v>
+        <v>0.121</v>
       </c>
       <c r="J15" t="n">
-        <v>2.555</v>
+        <v>3.025</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1133</v>
+        <v>-0.1186</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.8325</v>
+        <v>-2.965</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.21</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3571</v>
+        <v>0.3585</v>
       </c>
       <c r="J17" t="n">
-        <v>8.9275</v>
+        <v>8.9625</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0745</v>
+        <v>0.0814</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8625</v>
+        <v>2.035</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.003</v>
+        <v>0.0021</v>
       </c>
       <c r="J19" t="n">
-        <v>0.075</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.153</v>
+        <v>-0.1668</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.825</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2947</v>
+        <v>-0.3079</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.3675</v>
+        <v>-7.6975</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.22</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4843</v>
+        <v>0.4741</v>
       </c>
       <c r="J22" t="n">
-        <v>13.5604</v>
+        <v>13.2748</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3911</v>
+        <v>0.3878</v>
       </c>
       <c r="J23" t="n">
-        <v>10.9508</v>
+        <v>10.8584</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1314</v>
+        <v>-0.1447</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.6792</v>
+        <v>-4.0516</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1532</v>
+        <v>-0.167</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2896</v>
+        <v>-4.676</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3333</v>
+        <v>-0.3453</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.3324</v>
+        <v>-9.6684</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.162</v>
+        <v>1.1641</v>
       </c>
       <c r="J27" t="n">
-        <v>32.536</v>
+        <v>32.5948</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8884</v>
+        <v>0.8314</v>
       </c>
       <c r="J28" t="n">
-        <v>24.8752</v>
+        <v>23.2792</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2913</v>
+        <v>0.2957</v>
       </c>
       <c r="J29" t="n">
-        <v>8.1564</v>
+        <v>8.2796</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3545</v>
+        <v>-0.3393</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.926</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6349</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.096</v>
+        <v>-17.7772</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.88</v>
       </c>
       <c r="I32" t="n">
-        <v>0.963</v>
+        <v>0.9494</v>
       </c>
       <c r="J32" t="n">
-        <v>21.186</v>
+        <v>20.8868</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.68</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7684</v>
       </c>
       <c r="J33" t="n">
-        <v>16.9554</v>
+        <v>16.9048</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.41</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4972</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>10.9384</v>
+        <v>11.2552</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.22</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2832</v>
+        <v>0.3057</v>
       </c>
       <c r="J35" t="n">
-        <v>6.2304</v>
+        <v>6.7254</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1162</v>
+        <v>-0.1175</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.5564</v>
+        <v>-2.585</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.02</v>
       </c>
       <c r="I37" t="n">
-        <v>0.124</v>
+        <v>0.1125</v>
       </c>
       <c r="J37" t="n">
-        <v>2.728</v>
+        <v>2.475</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.86</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.143</v>
+        <v>-0.1644</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.146</v>
+        <v>-3.6168</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1862</v>
+        <v>-0.2072</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.0964</v>
+        <v>-4.5584</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.76</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2464</v>
+        <v>-0.2665</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.4208</v>
+        <v>-5.863</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.21</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7457</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.621</v>
+        <v>-16.4054</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.7</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1232</v>
+        <v>1.1318</v>
       </c>
       <c r="J42" t="n">
-        <v>31.4496</v>
+        <v>31.6904</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2636</v>
+        <v>0.2744</v>
       </c>
       <c r="J43" t="n">
-        <v>7.3808</v>
+        <v>7.6832</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0623</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.7444</v>
+        <v>-1.8928</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.96</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0757</v>
+        <v>-0.0822</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.1196</v>
+        <v>-2.3016</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1908</v>
+        <v>-0.2013</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.3424</v>
+        <v>-5.6364</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1454</v>
+        <v>1.1344</v>
       </c>
       <c r="J47" t="n">
-        <v>32.0712</v>
+        <v>31.7632</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3884</v>
+        <v>0.382</v>
       </c>
       <c r="J48" t="n">
-        <v>10.8752</v>
+        <v>10.696</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3608</v>
+        <v>0.3567</v>
       </c>
       <c r="J49" t="n">
-        <v>10.1024</v>
+        <v>9.9876</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4488</v>
+        <v>-0.4299</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.5664</v>
+        <v>-12.0372</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9129</v>
+        <v>-0.8407</v>
       </c>
       <c r="J51" t="n">
-        <v>-25.5612</v>
+        <v>-23.5396</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.28</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6075</v>
+        <v>0.6672</v>
       </c>
       <c r="J52" t="n">
-        <v>15.795</v>
+        <v>17.3472</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2161</v>
+        <v>0.2216</v>
       </c>
       <c r="J53" t="n">
-        <v>5.6186</v>
+        <v>5.7616</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0837</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>2.1762</v>
+        <v>2.4128</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0837</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>2.1762</v>
+        <v>2.4128</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3931</v>
+        <v>-0.3791</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.2206</v>
+        <v>-9.8566</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4235</v>
+        <v>0.4707</v>
       </c>
       <c r="J57" t="n">
-        <v>11.011</v>
+        <v>12.2382</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.21</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3925</v>
+        <v>0.4312</v>
       </c>
       <c r="J58" t="n">
-        <v>10.205</v>
+        <v>11.2112</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2684</v>
+        <v>0.2778</v>
       </c>
       <c r="J59" t="n">
-        <v>6.9784</v>
+        <v>7.2228</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.08</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1908</v>
+        <v>0.2023</v>
       </c>
       <c r="J60" t="n">
-        <v>4.9608</v>
+        <v>5.2598</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.278</v>
+        <v>-0.289</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.228</v>
+        <v>-7.514</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.69</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0998</v>
+        <v>1.205</v>
       </c>
       <c r="J62" t="n">
-        <v>28.5948</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.29</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5878</v>
+        <v>0.6532</v>
       </c>
       <c r="J63" t="n">
-        <v>15.2828</v>
+        <v>16.9832</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5201</v>
+        <v>0.5777</v>
       </c>
       <c r="J64" t="n">
-        <v>13.5226</v>
+        <v>15.0202</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0541</v>
+        <v>-0.0374</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.4066</v>
+        <v>-0.9724</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4376</v>
+        <v>-0.4103</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.3776</v>
+        <v>-10.6678</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.01</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0723</v>
+        <v>0.0683</v>
       </c>
       <c r="J67" t="n">
-        <v>1.8798</v>
+        <v>1.7758</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0347</v>
+        <v>-0.0464</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.9022</v>
+        <v>-1.2064</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0741</v>
+        <v>-0.0883</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.9266</v>
+        <v>-2.2958</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1625</v>
+        <v>-0.1794</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.225</v>
+        <v>-4.6644</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.53</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4777</v>
+        <v>-0.4858</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.4202</v>
+        <v>-12.6308</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.03</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1171</v>
+        <v>0.1183</v>
       </c>
       <c r="J72" t="n">
-        <v>3.3959</v>
+        <v>3.4307</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.96</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0538</v>
+        <v>-0.0653</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.5602</v>
+        <v>-1.8937</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1024</v>
+        <v>-0.1166</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.9696</v>
+        <v>-3.3814</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.5095</v>
+        <v>-4.9706</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3144</v>
+        <v>-0.3287</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.117599999999999</v>
+        <v>-9.532299999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8933</v>
+        <v>0.9843</v>
       </c>
       <c r="J77" t="n">
-        <v>25.9057</v>
+        <v>28.5447</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6586</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>19.0994</v>
+        <v>21.1787</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.21</v>
       </c>
       <c r="I79" t="n">
-        <v>0.481</v>
+        <v>0.533</v>
       </c>
       <c r="J79" t="n">
-        <v>13.949</v>
+        <v>15.457</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4246</v>
+        <v>0.4688</v>
       </c>
       <c r="J80" t="n">
-        <v>12.3134</v>
+        <v>13.5952</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7768</v>
+        <v>-0.7154</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.5272</v>
+        <v>-20.7466</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.96</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.026</v>
+        <v>-0.0437</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.624</v>
+        <v>-1.0488</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1798</v>
+        <v>-0.2</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.3152</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.77</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2396</v>
+        <v>-0.2593</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.7504</v>
+        <v>-6.2232</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.66</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3419</v>
+        <v>-0.359</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.2056</v>
+        <v>-8.616</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4355</v>
+        <v>-0.4482</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.452</v>
+        <v>-10.7568</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8206</v>
+        <v>0.9105</v>
       </c>
       <c r="J87" t="n">
-        <v>19.6944</v>
+        <v>21.852</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.38</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6944</v>
+        <v>0.7732</v>
       </c>
       <c r="J88" t="n">
-        <v>16.6656</v>
+        <v>18.5568</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5924</v>
+        <v>0.6605</v>
       </c>
       <c r="J89" t="n">
-        <v>14.2176</v>
+        <v>15.852</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.25</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5262</v>
+        <v>0.5865</v>
       </c>
       <c r="J90" t="n">
-        <v>12.6288</v>
+        <v>14.076</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.306</v>
+        <v>0.3192</v>
       </c>
       <c r="J91" t="n">
-        <v>7.344</v>
+        <v>7.6608</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7295</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>24.803</v>
+        <v>23.494</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3492</v>
+        <v>0.3488</v>
       </c>
       <c r="J93" t="n">
-        <v>11.8728</v>
+        <v>11.8592</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2952</v>
+        <v>0.2983</v>
       </c>
       <c r="J94" t="n">
-        <v>10.0368</v>
+        <v>10.1422</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2071</v>
+        <v>0.2156</v>
       </c>
       <c r="J95" t="n">
-        <v>7.0414</v>
+        <v>7.3304</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0239</v>
+        <v>-0.0164</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.8126</v>
+        <v>-0.5576</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.07</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1845</v>
+        <v>0.1922</v>
       </c>
       <c r="J97" t="n">
-        <v>6.273</v>
+        <v>6.5348</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.04</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1168</v>
+        <v>0.1251</v>
       </c>
       <c r="J98" t="n">
-        <v>3.9712</v>
+        <v>4.2534</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0383</v>
+        <v>0.0437</v>
       </c>
       <c r="J99" t="n">
-        <v>1.3022</v>
+        <v>1.4858</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0877</v>
+        <v>-0.0987</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.9818</v>
+        <v>-3.3558</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1112</v>
+        <v>-0.1233</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.7808</v>
+        <v>-4.1922</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.6</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2531</v>
+        <v>1.2262</v>
       </c>
       <c r="J102" t="n">
-        <v>33.8337</v>
+        <v>33.1074</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0517</v>
+        <v>1.0052</v>
       </c>
       <c r="J103" t="n">
-        <v>28.3959</v>
+        <v>27.1404</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5745</v>
+        <v>0.5603</v>
       </c>
       <c r="J104" t="n">
-        <v>15.5115</v>
+        <v>15.1281</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1382</v>
+        <v>0.1596</v>
       </c>
       <c r="J105" t="n">
-        <v>3.7314</v>
+        <v>4.3092</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1178</v>
+        <v>-0.1034</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.1806</v>
+        <v>-2.7918</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.06</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2106</v>
+        <v>0.2057</v>
       </c>
       <c r="J107" t="n">
-        <v>5.6862</v>
+        <v>5.5539</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1089</v>
+        <v>0.1045</v>
       </c>
       <c r="J108" t="n">
-        <v>2.9403</v>
+        <v>2.8215</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1611</v>
+        <v>-0.1784</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.3497</v>
+        <v>-4.8168</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.74</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2784</v>
+        <v>-0.2951</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.5168</v>
+        <v>-7.9677</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4663</v>
+        <v>-0.4754</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.5901</v>
+        <v>-12.8358</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.93</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0016</v>
+        <v>-0.0324</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0272</v>
+        <v>-0.5508</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1149</v>
+        <v>-0.1468</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.9533</v>
+        <v>-2.4956</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.48</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4791</v>
+        <v>-0.494</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.1447</v>
+        <v>-8.398</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.35</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6037</v>
+        <v>-0.6091</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.2629</v>
+        <v>-10.3547</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.28</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6718</v>
+        <v>-0.6713</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.4206</v>
+        <v>-11.4121</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.57</v>
       </c>
       <c r="I117" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J117" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3789</v>
+        <v>1.3717</v>
       </c>
       <c r="J118" t="n">
-        <v>23.4413</v>
+        <v>23.3189</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.31</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7398</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>12.5766</v>
+        <v>12.2451</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5048</v>
+        <v>0.5117</v>
       </c>
       <c r="J120" t="n">
-        <v>8.5816</v>
+        <v>8.6989</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.14</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3267</v>
+        <v>0.351</v>
       </c>
       <c r="J121" t="n">
-        <v>5.5539</v>
+        <v>5.967</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4218</v>
+        <v>0.4349</v>
       </c>
       <c r="J122" t="n">
-        <v>12.2322</v>
+        <v>12.6121</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.27</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3639</v>
+        <v>0.3793</v>
       </c>
       <c r="J123" t="n">
-        <v>10.5531</v>
+        <v>10.9997</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3639</v>
+        <v>0.3793</v>
       </c>
       <c r="J124" t="n">
-        <v>10.5531</v>
+        <v>10.9997</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2196</v>
+        <v>0.2377</v>
       </c>
       <c r="J125" t="n">
-        <v>6.3684</v>
+        <v>6.8933</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0189</v>
+        <v>-0.0146</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.5481</v>
+        <v>-0.4234</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3532</v>
+        <v>0.3529</v>
       </c>
       <c r="J127" t="n">
-        <v>10.2428</v>
+        <v>10.2341</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3388</v>
+        <v>0.3392</v>
       </c>
       <c r="J128" t="n">
-        <v>9.825200000000001</v>
+        <v>9.8368</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.726</v>
+        <v>-3.1001</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2413</v>
+        <v>-0.2563</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.9977</v>
+        <v>-7.4327</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4498</v>
+        <v>-0.4579</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.0442</v>
+        <v>-13.2791</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3748</v>
+        <v>0.368</v>
       </c>
       <c r="J132" t="n">
-        <v>8.6204</v>
+        <v>8.464</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0118</v>
+        <v>-0.0186</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.2714</v>
+        <v>-0.4278</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1057</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.1229</v>
+        <v>-2.4311</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2284</v>
+        <v>-0.2441</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.2532</v>
+        <v>-5.6143</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3352</v>
+        <v>-0.3486</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.7096</v>
+        <v>-8.017799999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.56</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1891</v>
+        <v>1.1607</v>
       </c>
       <c r="J137" t="n">
-        <v>27.3493</v>
+        <v>26.6961</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.45</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0528</v>
+        <v>1.0094</v>
       </c>
       <c r="J138" t="n">
-        <v>24.2144</v>
+        <v>23.2162</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.39</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9584</v>
+        <v>0.9065</v>
       </c>
       <c r="J139" t="n">
-        <v>22.0432</v>
+        <v>20.8495</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.356</v>
+        <v>0.3659</v>
       </c>
       <c r="J140" t="n">
-        <v>8.188000000000001</v>
+        <v>8.415699999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2731</v>
+        <v>0.2898</v>
       </c>
       <c r="J141" t="n">
-        <v>6.2813</v>
+        <v>6.6654</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.32</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4624</v>
+        <v>0.4659</v>
       </c>
       <c r="J142" t="n">
-        <v>13.872</v>
+        <v>13.977</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.17</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2714</v>
+        <v>0.2827</v>
       </c>
       <c r="J143" t="n">
-        <v>8.141999999999999</v>
+        <v>8.481</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0506</v>
+        <v>-0.0586</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.518</v>
+        <v>-1.758</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.199</v>
+        <v>-0.2124</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.97</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3083</v>
+        <v>-0.3204</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.249000000000001</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0136</v>
+        <v>0.9799</v>
       </c>
       <c r="J147" t="n">
-        <v>30.408</v>
+        <v>29.397</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5555</v>
+        <v>0.5528</v>
       </c>
       <c r="J148" t="n">
-        <v>16.665</v>
+        <v>16.584</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3818</v>
+        <v>0.3903</v>
       </c>
       <c r="J149" t="n">
-        <v>11.454</v>
+        <v>11.709</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2969</v>
+        <v>-0.3058</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.907</v>
+        <v>-9.173999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.66</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3909</v>
+        <v>-0.3975</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.727</v>
+        <v>-11.925</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.87</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1199</v>
+        <v>-0.1439</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.398</v>
+        <v>-2.878</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1315</v>
+        <v>-0.1553</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.63</v>
+        <v>-3.106</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.65</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3409</v>
+        <v>-0.36</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.818</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4246</v>
+        <v>-0.4397</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.492000000000001</v>
+        <v>-8.794</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4808</v>
+        <v>-0.4925</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.616</v>
+        <v>-9.85</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.68</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3134</v>
+        <v>1.2971</v>
       </c>
       <c r="J157" t="n">
-        <v>26.268</v>
+        <v>25.942</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2311</v>
+        <v>1.2092</v>
       </c>
       <c r="J158" t="n">
-        <v>24.622</v>
+        <v>24.184</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0764</v>
+        <v>1.0407</v>
       </c>
       <c r="J159" t="n">
-        <v>21.528</v>
+        <v>20.814</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.24</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6108</v>
+        <v>0.5998</v>
       </c>
       <c r="J160" t="n">
-        <v>12.216</v>
+        <v>11.996</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.14</v>
       </c>
       <c r="I161" t="n">
-        <v>0.36</v>
+        <v>0.3744</v>
       </c>
       <c r="J161" t="n">
-        <v>7.2</v>
+        <v>7.488</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.17</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4107</v>
+        <v>0.4022</v>
       </c>
       <c r="J162" t="n">
-        <v>10.2675</v>
+        <v>10.055</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="J163" t="n">
-        <v>9.289999999999999</v>
+        <v>9.1425</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0129</v>
+        <v>-0.0194</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.3225</v>
+        <v>-0.485</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.73</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.298</v>
+        <v>-0.3123</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.45</v>
+        <v>-7.8075</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4571</v>
+        <v>-0.4652</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.4275</v>
+        <v>-11.63</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.92</v>
+        <v>0.8581</v>
       </c>
       <c r="J167" t="n">
-        <v>23</v>
+        <v>21.4525</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.07</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2378</v>
+        <v>0.2445</v>
       </c>
       <c r="J168" t="n">
-        <v>5.945</v>
+        <v>6.1125</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1762</v>
+        <v>0.186</v>
       </c>
       <c r="J169" t="n">
-        <v>4.405</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.03</v>
       </c>
       <c r="I170" t="n">
-        <v>0.109</v>
+        <v>0.1212</v>
       </c>
       <c r="J170" t="n">
-        <v>2.725</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.02</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0721</v>
+        <v>0.0848</v>
       </c>
       <c r="J171" t="n">
-        <v>1.8025</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9699</v>
+        <v>0.9005</v>
       </c>
       <c r="J172" t="n">
-        <v>29.097</v>
+        <v>27.015</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2195</v>
+        <v>0.2239</v>
       </c>
       <c r="J173" t="n">
-        <v>6.585</v>
+        <v>6.717</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0473</v>
+        <v>0.0546</v>
       </c>
       <c r="J174" t="n">
-        <v>1.419</v>
+        <v>1.638</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1736</v>
+        <v>-0.1751</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.208</v>
+        <v>-5.253</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6318</v>
+        <v>-0.5949</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.954</v>
+        <v>-17.847</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.37</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7347</v>
+        <v>0.704</v>
       </c>
       <c r="J177" t="n">
-        <v>22.041</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1605</v>
+        <v>0.1692</v>
       </c>
       <c r="J178" t="n">
-        <v>4.815</v>
+        <v>5.076</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1123</v>
+        <v>-0.1241</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.369</v>
+        <v>-3.723</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1782</v>
+        <v>-0.1914</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.346</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2195</v>
+        <v>-0.2329</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.585</v>
+        <v>-6.987</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2762</v>
+        <v>1.2511</v>
       </c>
       <c r="J182" t="n">
-        <v>33.1812</v>
+        <v>32.5286</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6209</v>
+        <v>0.6021</v>
       </c>
       <c r="J183" t="n">
-        <v>16.1434</v>
+        <v>15.6546</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.21</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5733</v>
+        <v>0.5595</v>
       </c>
       <c r="J184" t="n">
-        <v>14.9058</v>
+        <v>14.547</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5491</v>
+        <v>0.5377</v>
       </c>
       <c r="J185" t="n">
-        <v>14.2766</v>
+        <v>13.9802</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1686</v>
+        <v>0.1889</v>
       </c>
       <c r="J186" t="n">
-        <v>4.3836</v>
+        <v>4.9114</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3173</v>
+        <v>0.3089</v>
       </c>
       <c r="J187" t="n">
-        <v>8.2498</v>
+        <v>8.0314</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0023</v>
+        <v>-0.0112</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.0598</v>
+        <v>-0.2912</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.86</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.162</v>
+        <v>-0.1791</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.212</v>
+        <v>-4.6566</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.66</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.356</v>
+        <v>-0.37</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.256</v>
+        <v>-9.619999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.65</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3654</v>
+        <v>-0.3791</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.500400000000001</v>
+        <v>-9.8566</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.94</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6357</v>
+        <v>1.6333</v>
       </c>
       <c r="J192" t="n">
-        <v>37.6211</v>
+        <v>37.5659</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.47</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0757</v>
+        <v>1.0371</v>
       </c>
       <c r="J193" t="n">
-        <v>24.7411</v>
+        <v>23.8533</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.29</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="J194" t="n">
-        <v>17.1235</v>
+        <v>16.445</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.1</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2695</v>
+        <v>0.2872</v>
       </c>
       <c r="J195" t="n">
-        <v>6.1985</v>
+        <v>6.6056</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4072</v>
+        <v>-0.3764</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.365600000000001</v>
+        <v>-8.6572</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1294</v>
+        <v>0.1273</v>
       </c>
       <c r="J197" t="n">
-        <v>2.9762</v>
+        <v>2.9279</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.98</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.02</v>
+        <v>-0.0304</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.46</v>
+        <v>-0.6992</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.93</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0863</v>
+        <v>-0.101</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.9849</v>
+        <v>-2.323</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.75</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2711</v>
+        <v>-0.2875</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.2353</v>
+        <v>-6.6125</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3946</v>
+        <v>-0.4068</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.075799999999999</v>
+        <v>-9.356400000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2679</v>
+        <v>1.2415</v>
       </c>
       <c r="J202" t="n">
-        <v>31.6975</v>
+        <v>31.0375</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.25</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6446</v>
       </c>
       <c r="J203" t="n">
-        <v>16.7225</v>
+        <v>16.115</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5523</v>
+        <v>0.5399</v>
       </c>
       <c r="J204" t="n">
-        <v>13.8075</v>
+        <v>13.4975</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4525</v>
+        <v>0.4499</v>
       </c>
       <c r="J205" t="n">
-        <v>11.3125</v>
+        <v>11.2475</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.02</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0355</v>
+        <v>0.0594</v>
       </c>
       <c r="J206" t="n">
-        <v>0.8875</v>
+        <v>1.485</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4215</v>
+        <v>0.4101</v>
       </c>
       <c r="J207" t="n">
-        <v>10.5375</v>
+        <v>10.2525</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3418</v>
+        <v>0.3356</v>
       </c>
       <c r="J208" t="n">
-        <v>8.545</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1654</v>
+        <v>-0.1816</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.135</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2558</v>
+        <v>-0.2716</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.395</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.54</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4724</v>
+        <v>-0.4802</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.81</v>
+        <v>-12.005</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.28</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7624</v>
+        <v>0.7227</v>
       </c>
       <c r="J212" t="n">
-        <v>19.8224</v>
+        <v>18.7902</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.21</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="J213" t="n">
-        <v>15.4518</v>
+        <v>14.9162</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4211</v>
+        <v>0.4167</v>
       </c>
       <c r="J214" t="n">
-        <v>10.9486</v>
+        <v>10.8342</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2274</v>
+        <v>0.2373</v>
       </c>
       <c r="J215" t="n">
-        <v>5.9124</v>
+        <v>6.1698</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.04</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1322</v>
+        <v>0.1468</v>
       </c>
       <c r="J216" t="n">
-        <v>3.4372</v>
+        <v>3.8168</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.49</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9807</v>
+        <v>0.9221</v>
       </c>
       <c r="J217" t="n">
-        <v>25.4982</v>
+        <v>23.9746</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.95</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0679</v>
+        <v>-0.08</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.7654</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.86</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1669</v>
+        <v>-0.1827</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.3394</v>
+        <v>-4.7502</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.73</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2965</v>
+        <v>-0.3111</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.709</v>
+        <v>-8.0886</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.51</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5013</v>
+        <v>-0.5072</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.0338</v>
+        <v>-13.1872</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.02</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0658</v>
+        <v>0.0688</v>
       </c>
       <c r="J222" t="n">
-        <v>1.4476</v>
+        <v>1.5136</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.98</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0277</v>
+        <v>-0.0364</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.8008</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0277</v>
+        <v>-0.0364</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.8008</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1673</v>
+        <v>-0.1831</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.6806</v>
+        <v>-4.0282</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3066</v>
+        <v>-0.3208</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.7452</v>
+        <v>-7.0576</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.57</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6884</v>
+        <v>0.6871</v>
       </c>
       <c r="J227" t="n">
-        <v>15.1448</v>
+        <v>15.1162</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.31</v>
       </c>
       <c r="I228" t="n">
-        <v>0.404</v>
+        <v>0.4191</v>
       </c>
       <c r="J228" t="n">
-        <v>8.888</v>
+        <v>9.2202</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2141</v>
+        <v>0.2336</v>
       </c>
       <c r="J229" t="n">
-        <v>4.7102</v>
+        <v>5.1392</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.14</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2009</v>
+        <v>0.2205</v>
       </c>
       <c r="J230" t="n">
-        <v>4.4198</v>
+        <v>4.851</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.09</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1316</v>
+        <v>0.151</v>
       </c>
       <c r="J231" t="n">
-        <v>2.8952</v>
+        <v>3.322</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0613</v>
+        <v>1.0145</v>
       </c>
       <c r="J232" t="n">
-        <v>30.7777</v>
+        <v>29.4205</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5654</v>
       </c>
       <c r="J233" t="n">
-        <v>16.8838</v>
+        <v>16.3966</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.18</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5103</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>14.7987</v>
+        <v>14.5145</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.18</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5103</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>14.7987</v>
+        <v>14.5145</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1494</v>
+        <v>0.1674</v>
       </c>
       <c r="J236" t="n">
-        <v>4.3326</v>
+        <v>4.8546</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.12</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3129</v>
+        <v>0.3102</v>
       </c>
       <c r="J237" t="n">
-        <v>9.0741</v>
+        <v>8.995799999999999</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.08</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2287</v>
+        <v>0.2297</v>
       </c>
       <c r="J238" t="n">
-        <v>6.6323</v>
+        <v>6.6613</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1255</v>
+        <v>-0.1402</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.6395</v>
+        <v>-4.0658</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2586</v>
+        <v>-0.2738</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.4994</v>
+        <v>-7.9402</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3167</v>
+        <v>-0.3306</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.1843</v>
+        <v>-9.587400000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4155</v>
+        <v>0.4233</v>
       </c>
       <c r="J242" t="n">
-        <v>14.958</v>
+        <v>15.2388</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1682</v>
+        <v>0.1821</v>
       </c>
       <c r="J243" t="n">
-        <v>6.0552</v>
+        <v>6.5556</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0227</v>
+        <v>0.0291</v>
       </c>
       <c r="J244" t="n">
-        <v>0.8172</v>
+        <v>1.0476</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.93</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1049</v>
+        <v>-0.1153</v>
       </c>
       <c r="J245" t="n">
-        <v>-3.7764</v>
+        <v>-4.1508</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1393</v>
+        <v>-0.1509</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.0148</v>
+        <v>-5.4324</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4069</v>
+        <v>0.4116</v>
       </c>
       <c r="J247" t="n">
-        <v>14.6484</v>
+        <v>14.8176</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3676</v>
+        <v>0.3745</v>
       </c>
       <c r="J248" t="n">
-        <v>13.2336</v>
+        <v>13.482</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.05</v>
       </c>
       <c r="I249" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1072</v>
       </c>
       <c r="J249" t="n">
-        <v>3.4092</v>
+        <v>3.8592</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.03</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0584</v>
+        <v>0.0697</v>
       </c>
       <c r="J250" t="n">
-        <v>2.1024</v>
+        <v>2.5092</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.0993</v>
+        <v>-0.1077</v>
       </c>
       <c r="J251" t="n">
-        <v>-3.5748</v>
+        <v>-3.8772</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.18</v>
       </c>
       <c r="I252" t="n">
-        <v>0.441</v>
+        <v>0.4282</v>
       </c>
       <c r="J252" t="n">
-        <v>10.584</v>
+        <v>10.2768</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1679</v>
+        <v>0.1687</v>
       </c>
       <c r="J253" t="n">
-        <v>4.0296</v>
+        <v>4.0488</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.92</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.102</v>
+        <v>-0.1163</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.448</v>
+        <v>-2.7912</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.72</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3043</v>
+        <v>-0.319</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.3032</v>
+        <v>-7.656</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4173</v>
+        <v>-0.4278</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.0152</v>
+        <v>-10.2672</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.72</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3954</v>
+        <v>1.3779</v>
       </c>
       <c r="J257" t="n">
-        <v>33.4896</v>
+        <v>33.0696</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.37</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.8771</v>
       </c>
       <c r="J258" t="n">
-        <v>22.3176</v>
+        <v>21.0504</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.17</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4723</v>
+        <v>0.469</v>
       </c>
       <c r="J259" t="n">
-        <v>11.3352</v>
+        <v>11.256</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2564</v>
+        <v>0.2716</v>
       </c>
       <c r="J260" t="n">
-        <v>6.1536</v>
+        <v>6.5184</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.02</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0293</v>
+        <v>0.055</v>
       </c>
       <c r="J261" t="n">
-        <v>0.7032</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.27</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6135</v>
+        <v>0.5856</v>
       </c>
       <c r="J262" t="n">
-        <v>15.951</v>
+        <v>15.2256</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0934</v>
+        <v>0.0931</v>
       </c>
       <c r="J263" t="n">
-        <v>2.4284</v>
+        <v>2.4206</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.98</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0243</v>
+        <v>-0.0338</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.6318</v>
+        <v>-0.8788</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.7</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3226</v>
+        <v>-0.337</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.387600000000001</v>
+        <v>-8.762</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.47</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5352</v>
+        <v>-0.5395</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.9152</v>
+        <v>-14.027</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.52</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1522</v>
+        <v>1.1186</v>
       </c>
       <c r="J267" t="n">
-        <v>29.9572</v>
+        <v>29.0836</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9715</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="J268" t="n">
-        <v>25.259</v>
+        <v>23.8368</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.26</v>
       </c>
       <c r="I269" t="n">
-        <v>0.6896</v>
+        <v>0.6635</v>
       </c>
       <c r="J269" t="n">
-        <v>17.9296</v>
+        <v>17.251</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.09</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2588</v>
+        <v>0.2733</v>
       </c>
       <c r="J270" t="n">
-        <v>6.7288</v>
+        <v>7.1058</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.06</v>
       </c>
       <c r="I271" t="n">
-        <v>0.1686</v>
+        <v>0.1889</v>
       </c>
       <c r="J271" t="n">
-        <v>4.3836</v>
+        <v>4.9114</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.85</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5235</v>
+        <v>1.5171</v>
       </c>
       <c r="J272" t="n">
-        <v>33.517</v>
+        <v>33.3762</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.52</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1324</v>
+        <v>1.1012</v>
       </c>
       <c r="J273" t="n">
-        <v>24.9128</v>
+        <v>24.2264</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.3</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7614</v>
+        <v>0.731</v>
       </c>
       <c r="J274" t="n">
-        <v>16.7508</v>
+        <v>16.082</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.17</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4507</v>
+        <v>0.454</v>
       </c>
       <c r="J275" t="n">
-        <v>9.9154</v>
+        <v>9.988</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>0.007</v>
+        <v>0.0394</v>
       </c>
       <c r="J276" t="n">
-        <v>0.154</v>
+        <v>0.8668</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.03</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1846</v>
+        <v>0.1679</v>
       </c>
       <c r="J277" t="n">
-        <v>4.0612</v>
+        <v>3.6938</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.77</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2382</v>
+        <v>-0.2581</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.2404</v>
+        <v>-5.6782</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.72</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.284</v>
+        <v>-0.3033</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.248</v>
+        <v>-6.6726</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.67</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3307</v>
+        <v>-0.3486</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.2754</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.53</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4617</v>
+        <v>-0.4732</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.1574</v>
+        <v>-10.4104</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.58</v>
       </c>
       <c r="I282" t="n">
-        <v>1.209</v>
+        <v>1.1828</v>
       </c>
       <c r="J282" t="n">
-        <v>25.389</v>
+        <v>24.8388</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.53</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1481</v>
+        <v>1.1175</v>
       </c>
       <c r="J283" t="n">
-        <v>24.1101</v>
+        <v>23.4675</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.35</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8736</v>
+        <v>0.8294</v>
       </c>
       <c r="J284" t="n">
-        <v>18.3456</v>
+        <v>17.4174</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.17</v>
       </c>
       <c r="I285" t="n">
-        <v>0.4555</v>
+        <v>0.4573</v>
       </c>
       <c r="J285" t="n">
-        <v>9.5655</v>
+        <v>9.603300000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.12</v>
       </c>
       <c r="I286" t="n">
-        <v>0.3234</v>
+        <v>0.3373</v>
       </c>
       <c r="J286" t="n">
-        <v>6.7914</v>
+        <v>7.0833</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.95</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0267</v>
+        <v>-0.0478</v>
       </c>
       <c r="J287" t="n">
-        <v>-0.5607</v>
+        <v>-1.0038</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1704</v>
+        <v>-0.1927</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.5784</v>
+        <v>-4.0467</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.73</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2715</v>
+        <v>-0.2919</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.7015</v>
+        <v>-6.1299</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4283</v>
+        <v>-0.4425</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.994300000000001</v>
+        <v>-9.2925</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.503</v>
+        <v>-0.5128</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.563</v>
+        <v>-10.7688</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3172</v>
+        <v>1.2875</v>
       </c>
       <c r="J292" t="n">
-        <v>38.1988</v>
+        <v>37.3375</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.39</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0106</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>29.3074</v>
+        <v>27.5529</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3986</v>
+        <v>0.3952</v>
       </c>
       <c r="J294" t="n">
-        <v>11.5594</v>
+        <v>11.4608</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.84</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5507</v>
+        <v>-0.5178</v>
       </c>
       <c r="J295" t="n">
-        <v>-15.9703</v>
+        <v>-15.0162</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.64</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.0513</v>
+        <v>-0.9576</v>
       </c>
       <c r="J296" t="n">
-        <v>-30.4877</v>
+        <v>-27.7704</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.26</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5208</v>
       </c>
       <c r="J297" t="n">
-        <v>15.3613</v>
+        <v>15.1032</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.24</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4947</v>
+        <v>0.4886</v>
       </c>
       <c r="J298" t="n">
-        <v>14.3463</v>
+        <v>14.1694</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.11</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2548</v>
+        <v>0.2633</v>
       </c>
       <c r="J299" t="n">
-        <v>7.3892</v>
+        <v>7.6357</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.87</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1727</v>
+        <v>-0.1847</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.0083</v>
+        <v>-5.3563</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2648</v>
+        <v>-0.2767</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.6792</v>
+        <v>-8.0243</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0121</v>
+        <v>0.0089</v>
       </c>
       <c r="J302" t="n">
-        <v>0.3267</v>
+        <v>0.2403</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0126</v>
+        <v>-0.0192</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.3402</v>
+        <v>-0.5184</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.96</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0563</v>
+        <v>-0.0673</v>
       </c>
       <c r="J304" t="n">
-        <v>-1.5201</v>
+        <v>-1.8171</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.91</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1148</v>
+        <v>-0.1291</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.0996</v>
+        <v>-3.4857</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2977</v>
+        <v>-0.3121</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.0379</v>
+        <v>-8.4267</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.75</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8915</v>
+        <v>0.8721</v>
       </c>
       <c r="J307" t="n">
-        <v>24.0705</v>
+        <v>23.5467</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.29</v>
       </c>
       <c r="I308" t="n">
-        <v>0.388</v>
+        <v>0.4024</v>
       </c>
       <c r="J308" t="n">
-        <v>10.476</v>
+        <v>10.8648</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.11</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1666</v>
+        <v>0.1847</v>
       </c>
       <c r="J309" t="n">
-        <v>4.4982</v>
+        <v>4.9869</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.0183</v>
+        <v>-0.0141</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.4941</v>
+        <v>-0.3807</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.83</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2292</v>
+        <v>-0.2383</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.1884</v>
+        <v>-6.4341</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.33</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9173</v>
+        <v>0.8521</v>
       </c>
       <c r="J312" t="n">
-        <v>26.6017</v>
+        <v>24.7109</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.22</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6488</v>
+        <v>0.6163</v>
       </c>
       <c r="J313" t="n">
-        <v>18.8152</v>
+        <v>17.8727</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.16</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4945</v>
+        <v>0.4786</v>
       </c>
       <c r="J314" t="n">
-        <v>14.3405</v>
+        <v>13.8794</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.96</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.179</v>
+        <v>-0.1788</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.191</v>
+        <v>-5.1852</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.1062</v>
+        <v>-1.0073</v>
       </c>
       <c r="J316" t="n">
-        <v>-32.0798</v>
+        <v>-29.2117</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4023</v>
+        <v>0.3997</v>
       </c>
       <c r="J317" t="n">
-        <v>11.6667</v>
+        <v>11.5913</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2263</v>
+        <v>0.233</v>
       </c>
       <c r="J318" t="n">
-        <v>6.5627</v>
+        <v>6.757</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0757</v>
+        <v>-0.0859</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.1953</v>
+        <v>-2.4911</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.93</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.0998</v>
+        <v>-0.1113</v>
       </c>
       <c r="J320" t="n">
-        <v>-2.8942</v>
+        <v>-3.2277</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.84</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1981</v>
+        <v>-0.2117</v>
       </c>
       <c r="J321" t="n">
-        <v>-5.7449</v>
+        <v>-6.1393</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.16</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3897</v>
+        <v>0.3829</v>
       </c>
       <c r="J322" t="n">
-        <v>10.5219</v>
+        <v>10.3383</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.96</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.057</v>
+        <v>-0.0678</v>
       </c>
       <c r="J323" t="n">
-        <v>-1.539</v>
+        <v>-1.8306</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J324" t="n">
-        <v>-2.2059</v>
+        <v>-2.5434</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1996</v>
+        <v>-0.2152</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.3892</v>
+        <v>-5.8104</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.73</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2985</v>
+        <v>-0.3127</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.0595</v>
+        <v>-8.4429</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.56</v>
       </c>
       <c r="I327" t="n">
-        <v>1.2121</v>
+        <v>1.1809</v>
       </c>
       <c r="J327" t="n">
-        <v>32.7267</v>
+        <v>31.8843</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.35</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8481</v>
       </c>
       <c r="J328" t="n">
-        <v>24.3189</v>
+        <v>22.8987</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.07</v>
       </c>
       <c r="I329" t="n">
-        <v>0.2096</v>
+        <v>0.225</v>
       </c>
       <c r="J329" t="n">
-        <v>5.6592</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.07</v>
       </c>
       <c r="I330" t="n">
-        <v>0.2096</v>
+        <v>0.225</v>
       </c>
       <c r="J330" t="n">
-        <v>5.6592</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.06</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1788</v>
+        <v>0.1959</v>
       </c>
       <c r="J331" t="n">
-        <v>4.8276</v>
+        <v>5.2893</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.34</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6701</v>
+        <v>0.648</v>
       </c>
       <c r="J332" t="n">
-        <v>27.4741</v>
+        <v>26.568</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3339</v>
+        <v>0.3381</v>
       </c>
       <c r="J333" t="n">
-        <v>13.6899</v>
+        <v>13.8621</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.91</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1277</v>
+        <v>-0.139</v>
       </c>
       <c r="J334" t="n">
-        <v>-5.2357</v>
+        <v>-5.699</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.91</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1277</v>
+        <v>-0.139</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.2357</v>
+        <v>-5.699</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.9</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1389</v>
+        <v>-0.1505</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.6949</v>
+        <v>-6.1705</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.18</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5525</v>
+        <v>0.5295</v>
       </c>
       <c r="J337" t="n">
-        <v>22.6525</v>
+        <v>21.7095</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5</v>
+        <v>0.4824</v>
       </c>
       <c r="J338" t="n">
-        <v>20.5</v>
+        <v>19.7784</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.16</v>
       </c>
       <c r="I339" t="n">
-        <v>0.5</v>
+        <v>0.4824</v>
       </c>
       <c r="J339" t="n">
-        <v>20.5</v>
+        <v>19.7784</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.271</v>
+        <v>-0.2672</v>
       </c>
       <c r="J340" t="n">
-        <v>-11.111</v>
+        <v>-10.9552</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.77</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.664</v>
       </c>
       <c r="J341" t="n">
-        <v>-29.1182</v>
+        <v>-27.224</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5435/event_5435_evp_summary.xlsx
+++ b/database/event/5435/event_5435_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1917</v>
+        <v>6.0552</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2312</v>
+        <v>1.2041</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1944</v>
+        <v>2.1526</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1917</v>
+        <v>6.0552</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9043</v>
+        <v>3.7821</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2874</v>
+        <v>2.2731</v>
       </c>
       <c r="H2" t="n">
-        <v>7.9877</v>
+        <v>7.7572</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3133</v>
+        <v>4.3554</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2874</v>
+        <v>2.2731</v>
       </c>
       <c r="K2" t="n">
         <v>91</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6007</v>
+        <v>6.628500000000001</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1811</v>
+        <v>5.9744</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2291</v>
+        <v>1.188</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1896</v>
+        <v>2.1158</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1811</v>
+        <v>5.9744</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3207</v>
+        <v>3.2423</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8604</v>
+        <v>2.7321</v>
       </c>
       <c r="H3" t="n">
-        <v>6.0619</v>
+        <v>5.7303</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2734</v>
+        <v>3.2174</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8604</v>
+        <v>2.7321</v>
       </c>
       <c r="K3" t="n">
         <v>91</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1338</v>
+        <v>5.9495</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.116</v>
+        <v>5.8313</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2162</v>
+        <v>1.1596</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1599</v>
+        <v>2.0506</v>
       </c>
       <c r="E4" t="n">
-        <v>6.116</v>
+        <v>5.8313</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9547</v>
+        <v>2.9025</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1613</v>
+        <v>2.9288</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8545</v>
+        <v>4.4547</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6214</v>
+        <v>2.5012</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1613</v>
+        <v>2.9288</v>
       </c>
       <c r="K4" t="n">
         <v>195</v>
@@ -621,7 +621,7 @@
         <v>191</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7827</v>
+        <v>5.43</v>
       </c>
       <c r="N4" t="n">
         <v>386</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7781</v>
+        <v>5.451</v>
       </c>
       <c r="C5" t="n">
-        <v>1.149</v>
+        <v>1.084</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0061</v>
+        <v>1.8774</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7781</v>
+        <v>5.451</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5871</v>
+        <v>1.5148</v>
       </c>
       <c r="G5" t="n">
-        <v>4.191</v>
+        <v>3.9362</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5871</v>
+        <v>1.5148</v>
       </c>
       <c r="I5" t="n">
-        <v>0.857</v>
+        <v>0.8505</v>
       </c>
       <c r="J5" t="n">
-        <v>4.191</v>
+        <v>3.9362</v>
       </c>
       <c r="K5" t="n">
         <v>195</v>
@@ -667,7 +667,7 @@
         <v>191</v>
       </c>
       <c r="M5" t="n">
-        <v>5.048</v>
+        <v>4.7867</v>
       </c>
       <c r="N5" t="n">
         <v>386</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6006</v>
+        <v>4.466</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.8881</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4701</v>
+        <v>1.4287</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6006</v>
+        <v>4.466</v>
       </c>
       <c r="F6" t="n">
-        <v>2.537</v>
+        <v>2.5433</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0636</v>
+        <v>1.9227</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4762</v>
+        <v>3.106</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8771</v>
+        <v>1.7439</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0636</v>
+        <v>1.9227</v>
       </c>
       <c r="K6" t="n">
         <v>195</v>
@@ -713,7 +713,7 @@
         <v>191</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9407</v>
+        <v>3.6666</v>
       </c>
       <c r="N6" t="n">
         <v>386</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.058</v>
+        <v>3.9927</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2231</v>
+        <v>1.2131</v>
       </c>
       <c r="E7" t="n">
-        <v>4.058</v>
+        <v>3.9927</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4228</v>
+        <v>2.8552</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6352</v>
+        <v>1.1375</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3988</v>
+        <v>4.2772</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4553</v>
+        <v>2.4015</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6352</v>
+        <v>1.1375</v>
       </c>
       <c r="K7" t="n">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="L7" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0905</v>
+        <v>3.539</v>
       </c>
       <c r="N7" t="n">
-        <v>386</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0368</v>
+        <v>3.9475</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8027</v>
+        <v>0.785</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2134</v>
+        <v>1.1925</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0368</v>
+        <v>3.9475</v>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>3.3384</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1568</v>
+        <v>0.6091</v>
       </c>
       <c r="H8" t="n">
-        <v>4.608</v>
+        <v>6.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4883</v>
+        <v>3.42</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1568</v>
+        <v>0.6091</v>
       </c>
       <c r="K8" t="n">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="L8" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6451</v>
+        <v>4.0291</v>
       </c>
       <c r="N8" t="n">
-        <v>281</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.718</v>
+        <v>3.5523</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7393</v>
+        <v>0.7064</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0683</v>
+        <v>1.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>3.718</v>
+        <v>3.5523</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5285</v>
+        <v>3.3963</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1895</v>
+        <v>0.156</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7477</v>
+        <v>6.3086</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6437</v>
+        <v>3.5421</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1895</v>
+        <v>0.156</v>
       </c>
       <c r="K9" t="n">
         <v>193</v>
@@ -851,7 +851,7 @@
         <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8332</v>
+        <v>3.6981</v>
       </c>
       <c r="N9" t="n">
         <v>245</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6217</v>
+        <v>3.5261</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7202</v>
+        <v>0.7012</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0245</v>
+        <v>1.0005</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6217</v>
+        <v>3.5261</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3758</v>
+        <v>3.307</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2459</v>
+        <v>0.2191</v>
       </c>
       <c r="H10" t="n">
-        <v>6.244</v>
+        <v>5.9733</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3717</v>
+        <v>3.3538</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2459</v>
+        <v>0.2191</v>
       </c>
       <c r="K10" t="n">
         <v>91</v>
@@ -897,7 +897,7 @@
         <v>190</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6176</v>
+        <v>3.5729</v>
       </c>
       <c r="N10" t="n">
         <v>281</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5074</v>
+        <v>3.4452</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6975</v>
+        <v>0.6851</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9724</v>
+        <v>0.9637</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5074</v>
+        <v>3.4452</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4686</v>
+        <v>2.5124</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0388</v>
+        <v>0.9328</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2506</v>
+        <v>2.9898</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7553</v>
+        <v>1.6787</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0388</v>
+        <v>0.9328</v>
       </c>
       <c r="K11" t="n">
         <v>195</v>
@@ -943,7 +943,7 @@
         <v>191</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7941</v>
+        <v>2.6115</v>
       </c>
       <c r="N11" t="n">
         <v>386</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2051</v>
+        <v>3.1653</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6373</v>
+        <v>0.6294</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8348</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2051</v>
+        <v>3.1653</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5405</v>
+        <v>3.4735</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3354</v>
+        <v>-0.3082</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7873</v>
+        <v>6.5984</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6651</v>
+        <v>3.7048</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3354</v>
+        <v>-0.3082</v>
       </c>
       <c r="K12" t="n">
         <v>193</v>
@@ -989,7 +989,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3297</v>
+        <v>3.3966</v>
       </c>
       <c r="N12" t="n">
         <v>245</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9465</v>
+        <v>2.8741</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5859</v>
+        <v>0.5715</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7171</v>
+        <v>0.7035</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9465</v>
+        <v>2.8741</v>
       </c>
       <c r="F13" t="n">
-        <v>2.447</v>
+        <v>2.4485</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4995</v>
+        <v>0.4256</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1795</v>
+        <v>2.7501</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7169</v>
+        <v>1.5441</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4995</v>
+        <v>0.4256</v>
       </c>
       <c r="K13" t="n">
         <v>193</v>
@@ -1035,7 +1035,7 @@
         <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2164</v>
+        <v>1.9697</v>
       </c>
       <c r="N13" t="n">
         <v>245</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5813</v>
+        <v>2.601</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5133</v>
+        <v>0.5172</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5813</v>
+        <v>2.601</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5964</v>
+        <v>2.6612</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0151</v>
+        <v>-0.0602</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6723</v>
+        <v>3.5486</v>
       </c>
       <c r="I14" t="n">
-        <v>1.983</v>
+        <v>1.9924</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0151</v>
+        <v>-0.0602</v>
       </c>
       <c r="K14" t="n">
         <v>193</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9679</v>
+        <v>1.9322</v>
       </c>
       <c r="N14" t="n">
         <v>245</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4368</v>
+        <v>2.4369</v>
       </c>
       <c r="C15" t="n">
         <v>0.4846</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4851</v>
+        <v>0.5043</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4368</v>
+        <v>2.4369</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6775</v>
+        <v>2.6936</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2407</v>
+        <v>-0.2567</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9399</v>
+        <v>3.6704</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1275</v>
+        <v>2.0608</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2407</v>
+        <v>-0.2567</v>
       </c>
       <c r="K15" t="n">
         <v>145</v>
@@ -1127,7 +1127,7 @@
         <v>53</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8868</v>
+        <v>1.8041</v>
       </c>
       <c r="N15" t="n">
         <v>198</v>
@@ -1136,78 +1136,78 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2882</v>
+        <v>2.3491</v>
       </c>
       <c r="C16" t="n">
-        <v>0.455</v>
+        <v>0.4671</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4174</v>
+        <v>0.4643</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2882</v>
+        <v>2.3491</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2882</v>
+        <v>2.3466</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2882</v>
+        <v>2.3675</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2882</v>
+        <v>1.3293</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="K16" t="n">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2882</v>
+        <v>1.3318</v>
       </c>
       <c r="N16" t="n">
-        <v>222</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2467</v>
+        <v>2.2269</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4468</v>
+        <v>0.4428</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3985</v>
+        <v>0.4087</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2467</v>
+        <v>2.2269</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2467</v>
+        <v>2.2269</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2467</v>
+        <v>2.2269</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2467</v>
+        <v>2.2269</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2467</v>
+        <v>2.2269</v>
       </c>
       <c r="N17" t="n">
         <v>222</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2277</v>
+        <v>2.1589</v>
       </c>
       <c r="C18" t="n">
-        <v>0.443</v>
+        <v>0.4293</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3899</v>
+        <v>0.3777</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2277</v>
+        <v>2.1589</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2048</v>
+        <v>2.5032</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0229</v>
+        <v>-0.3443</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3804</v>
+        <v>2.9555</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2854</v>
+        <v>1.6594</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0229</v>
+        <v>-0.3443</v>
       </c>
       <c r="K18" t="n">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="L18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3083</v>
+        <v>1.3151</v>
       </c>
       <c r="N18" t="n">
-        <v>245</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1488</v>
+        <v>2.1458</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4273</v>
+        <v>0.4267</v>
       </c>
       <c r="D19" t="n">
-        <v>0.354</v>
+        <v>0.3717</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1488</v>
+        <v>2.1458</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7684</v>
+        <v>2.7393</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6196</v>
+        <v>-0.5935</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2397</v>
+        <v>3.8421</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2894</v>
+        <v>2.1572</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6196</v>
+        <v>-0.5935</v>
       </c>
       <c r="K19" t="n">
         <v>145</v>
@@ -1311,7 +1311,7 @@
         <v>53</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6698</v>
+        <v>1.5637</v>
       </c>
       <c r="N19" t="n">
         <v>198</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>leaf</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.117</v>
+        <v>2.1391</v>
       </c>
       <c r="C20" t="n">
-        <v>0.421</v>
+        <v>0.4254</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3395</v>
+        <v>0.3687</v>
       </c>
       <c r="E20" t="n">
-        <v>2.117</v>
+        <v>2.1391</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4894</v>
+        <v>2.1391</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3724</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3191</v>
+        <v>2.1391</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7923</v>
+        <v>2.1391</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3724</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="L20" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4199</v>
+        <v>2.1391</v>
       </c>
       <c r="N20" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8771</v>
+        <v>1.8039</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3733</v>
+        <v>0.3587</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2303</v>
+        <v>0.216</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8771</v>
+        <v>1.8039</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8771</v>
+        <v>1.8039</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8771</v>
+        <v>1.8039</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8771</v>
+        <v>1.8039</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8771</v>
+        <v>1.8039</v>
       </c>
       <c r="N21" t="n">
         <v>222</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5838</v>
+        <v>1.3838</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3149</v>
+        <v>0.2752</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0968</v>
+        <v>0.0246</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5838</v>
+        <v>1.3838</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5838</v>
+        <v>1.3838</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5838</v>
+        <v>1.3838</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5838</v>
+        <v>1.3838</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5838</v>
+        <v>1.3838</v>
       </c>
       <c r="N22" t="n">
         <v>141</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5383</v>
+        <v>1.3247</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3059</v>
+        <v>0.2634</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0761</v>
+        <v>-0.0023</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5383</v>
+        <v>1.3247</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5383</v>
+        <v>1.3247</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5383</v>
+        <v>1.3247</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5383</v>
+        <v>1.3247</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5383</v>
+        <v>1.3247</v>
       </c>
       <c r="N23" t="n">
         <v>141</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4878</v>
+        <v>1.2691</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2959</v>
+        <v>0.2524</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0531</v>
+        <v>-0.0277</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4878</v>
+        <v>1.2691</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4878</v>
+        <v>1.2691</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4878</v>
+        <v>1.2691</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4878</v>
+        <v>1.2691</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4878</v>
+        <v>1.2691</v>
       </c>
       <c r="N24" t="n">
         <v>231</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2947</v>
+        <v>1.1708</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2575</v>
+        <v>0.2328</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0348</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2947</v>
+        <v>1.1708</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6193</v>
+        <v>1.4678</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3246</v>
+        <v>-0.297</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6193</v>
+        <v>1.4678</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8744</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3246</v>
+        <v>-0.297</v>
       </c>
       <c r="K25" t="n">
         <v>145</v>
@@ -1587,7 +1587,7 @@
         <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5498</v>
+        <v>0.5271000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>198</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2017</v>
+        <v>1.1528</v>
       </c>
       <c r="C26" t="n">
-        <v>0.239</v>
+        <v>0.2292</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0772</v>
+        <v>-0.0806</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2017</v>
+        <v>1.1528</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2017</v>
+        <v>1.1528</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2017</v>
+        <v>1.1528</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2017</v>
+        <v>1.1528</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2017</v>
+        <v>1.1528</v>
       </c>
       <c r="N26" t="n">
         <v>222</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1142</v>
+        <v>1.0964</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2216</v>
+        <v>0.218</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.117</v>
+        <v>-0.1063</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1142</v>
+        <v>1.0964</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1142</v>
+        <v>1.0964</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1142</v>
+        <v>1.0964</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1142</v>
+        <v>1.0964</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1142</v>
+        <v>1.0964</v>
       </c>
       <c r="N27" t="n">
         <v>231</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0324</v>
+        <v>0.9778</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2053</v>
+        <v>0.1944</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1542</v>
+        <v>-0.1604</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0324</v>
+        <v>0.9778</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0324</v>
+        <v>0.9778</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0324</v>
+        <v>0.9778</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0324</v>
+        <v>0.9778</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0324</v>
+        <v>0.9778</v>
       </c>
       <c r="N28" t="n">
         <v>231</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8461</v>
+        <v>0.6186</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1683</v>
+        <v>0.123</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.239</v>
+        <v>-0.324</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8461</v>
+        <v>0.6186</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8461</v>
+        <v>0.6186</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8461</v>
+        <v>0.6186</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8461</v>
+        <v>0.6186</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8461</v>
+        <v>0.6186</v>
       </c>
       <c r="N29" t="n">
         <v>231</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5945</v>
+        <v>0.576</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1182</v>
+        <v>0.1145</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3536</v>
+        <v>-0.3434</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5945</v>
+        <v>0.576</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9111</v>
+        <v>0.8608</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3166</v>
+        <v>-0.2848</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9111</v>
+        <v>0.8608</v>
       </c>
       <c r="I30" t="n">
-        <v>0.492</v>
+        <v>0.4833</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3166</v>
+        <v>-0.2848</v>
       </c>
       <c r="K30" t="n">
         <v>145</v>
@@ -1817,7 +1817,7 @@
         <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1754</v>
+        <v>0.1985</v>
       </c>
       <c r="N30" t="n">
         <v>198</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2182</v>
+        <v>0.1991</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0434</v>
+        <v>0.0396</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5249</v>
+        <v>-0.5151</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2182</v>
+        <v>0.1991</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2182</v>
+        <v>0.1991</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2182</v>
+        <v>0.1991</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2182</v>
+        <v>0.1991</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2182</v>
+        <v>0.1991</v>
       </c>
       <c r="N31" t="n">
         <v>141</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0154</v>
+        <v>0.0002</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.589</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0219</v>
+        <v>0.96</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.9446</v>
+        <v>-0.9589</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0219</v>
+        <v>0.96</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5518</v>
+        <v>0.539</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9446</v>
+        <v>-0.9589</v>
       </c>
       <c r="K32" t="n">
         <v>91</v>
@@ -1909,7 +1909,7 @@
         <v>190</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3928</v>
+        <v>-0.4198999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>281</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3327</v>
+        <v>-0.3415</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0679</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.7614</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3327</v>
+        <v>-0.3415</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3327</v>
+        <v>-0.3415</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3327</v>
+        <v>-0.3415</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3327</v>
+        <v>-0.3415</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3327</v>
+        <v>-0.3415</v>
       </c>
       <c r="N33" t="n">
         <v>118</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3757</v>
+        <v>-0.4075</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0747</v>
+        <v>-0.081</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7952</v>
+        <v>-0.7914</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3757</v>
+        <v>-0.4075</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3757</v>
+        <v>-0.4075</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3757</v>
+        <v>-0.4075</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3757</v>
+        <v>-0.4075</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3757</v>
+        <v>-0.4075</v>
       </c>
       <c r="N34" t="n">
         <v>141</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4393</v>
+        <v>-0.5151</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1024</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8242</v>
+        <v>-0.8404</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4393</v>
+        <v>-0.5151</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4393</v>
+        <v>-0.5151</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4393</v>
+        <v>-0.5151</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4393</v>
+        <v>-0.5151</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4393</v>
+        <v>-0.5151</v>
       </c>
       <c r="N35" t="n">
         <v>118</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6963</v>
+        <v>-0.6743</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1385</v>
+        <v>-0.1341</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9412</v>
+        <v>-0.913</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6963</v>
+        <v>-0.6743</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6963</v>
+        <v>-0.6743</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6963</v>
+        <v>-0.6743</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6963</v>
+        <v>-0.6743</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6963</v>
+        <v>-0.6743</v>
       </c>
       <c r="N36" t="n">
         <v>118</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8438</v>
+        <v>-0.8665</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1678</v>
+        <v>-0.1723</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0083</v>
+        <v>-1.0005</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8438</v>
+        <v>-0.8665</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8438</v>
+        <v>-0.8665</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8438</v>
+        <v>-0.8665</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8438</v>
+        <v>-0.8665</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8438</v>
+        <v>-0.8665</v>
       </c>
       <c r="N37" t="n">
         <v>118</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0074</v>
+        <v>-0.9388</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2003</v>
+        <v>-0.1867</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0828</v>
+        <v>-1.0335</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0074</v>
+        <v>-0.9388</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0074</v>
+        <v>-0.9388</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0074</v>
+        <v>-0.9388</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0074</v>
+        <v>-0.9388</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0074</v>
+        <v>-0.9388</v>
       </c>
       <c r="N38" t="n">
-        <v>222</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0284</v>
+        <v>-0.9938</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2045</v>
+        <v>-0.1976</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0924</v>
+        <v>-1.0585</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0284</v>
+        <v>-0.9938</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0284</v>
+        <v>-0.9938</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0284</v>
+        <v>-0.9938</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0284</v>
+        <v>-0.9938</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>141</v>
+        <v>222</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0284</v>
+        <v>-0.9938</v>
       </c>
       <c r="N39" t="n">
-        <v>141</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8541</v>
+        <v>-1.7931</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3687</v>
+        <v>-0.3566</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4682</v>
+        <v>-1.4226</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8541</v>
+        <v>-1.7931</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8541</v>
+        <v>-1.7931</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8541</v>
+        <v>-1.7931</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8541</v>
+        <v>-1.7931</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8541</v>
+        <v>-1.7931</v>
       </c>
       <c r="N40" t="n">
         <v>118</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6193</v>
+        <v>-2.6</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5209</v>
+        <v>-0.517</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8166</v>
+        <v>-1.7902</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6193</v>
+        <v>-2.6</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6193</v>
+        <v>-2.6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6193</v>
+        <v>-2.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6193</v>
+        <v>-2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6193</v>
+        <v>-2.6</v>
       </c>
       <c r="N41" t="n">
         <v>231</v>
@@ -2429,10 +2429,10 @@
         <v>1.27</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5474</v>
+        <v>0.488</v>
       </c>
       <c r="J2" t="n">
-        <v>19.159</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4822</v>
+        <v>0.4234</v>
       </c>
       <c r="J3" t="n">
-        <v>16.877</v>
+        <v>14.819</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1903</v>
+        <v>0.1507</v>
       </c>
       <c r="J4" t="n">
-        <v>6.6605</v>
+        <v>5.2745</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.17</v>
+        <v>-0.1497</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.95</v>
+        <v>-5.2395</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4466</v>
+        <v>-0.4415</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.631</v>
+        <v>-15.4525</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7845</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>27.4575</v>
+        <v>26.516</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5955</v>
+        <v>0.5596</v>
       </c>
       <c r="J8" t="n">
-        <v>20.8425</v>
+        <v>19.586</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2922</v>
+        <v>0.2586</v>
       </c>
       <c r="J9" t="n">
-        <v>10.227</v>
+        <v>9.051</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2373</v>
+        <v>0.2064</v>
       </c>
       <c r="J10" t="n">
-        <v>8.3055</v>
+        <v>7.224</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1784</v>
+        <v>0.1513</v>
       </c>
       <c r="J11" t="n">
-        <v>6.244</v>
+        <v>5.2955</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.64</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7562</v>
+        <v>0.6843</v>
       </c>
       <c r="J12" t="n">
-        <v>18.905</v>
+        <v>17.1075</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5154</v>
+        <v>0.4473</v>
       </c>
       <c r="J13" t="n">
-        <v>12.885</v>
+        <v>11.1825</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2841</v>
+        <v>0.2344</v>
       </c>
       <c r="J14" t="n">
-        <v>7.1025</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.121</v>
+        <v>0.0924</v>
       </c>
       <c r="J15" t="n">
-        <v>3.025</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1186</v>
+        <v>-0.1013</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.965</v>
+        <v>-2.5325</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.21</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3585</v>
+        <v>0.3515</v>
       </c>
       <c r="J17" t="n">
-        <v>8.9625</v>
+        <v>8.7875</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0814</v>
+        <v>0.0672</v>
       </c>
       <c r="J18" t="n">
-        <v>2.035</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0021</v>
+        <v>0.0012</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0525</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1668</v>
+        <v>-0.1468</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.17</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3079</v>
+        <v>-0.2902</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.6975</v>
+        <v>-7.255</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.22</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4741</v>
+        <v>0.4159</v>
       </c>
       <c r="J22" t="n">
-        <v>13.2748</v>
+        <v>11.6452</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3878</v>
+        <v>0.3321</v>
       </c>
       <c r="J23" t="n">
-        <v>10.8584</v>
+        <v>9.2988</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1447</v>
+        <v>-0.1254</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0516</v>
+        <v>-3.5112</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.167</v>
+        <v>-0.147</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.676</v>
+        <v>-4.116</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3453</v>
+        <v>-0.3302</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.6684</v>
+        <v>-9.2456</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1641</v>
+        <v>1.1759</v>
       </c>
       <c r="J27" t="n">
-        <v>32.5948</v>
+        <v>32.9252</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8314</v>
+        <v>0.8075</v>
       </c>
       <c r="J28" t="n">
-        <v>23.2792</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2957</v>
+        <v>0.261</v>
       </c>
       <c r="J29" t="n">
-        <v>8.2796</v>
+        <v>7.308</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3393</v>
+        <v>-0.2974</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.500400000000001</v>
+        <v>-8.327199999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6349</v>
+        <v>-0.5998</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.7772</v>
+        <v>-16.7944</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.88</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9494</v>
+        <v>0.8815</v>
       </c>
       <c r="J32" t="n">
-        <v>20.8868</v>
+        <v>19.393</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.68</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7684</v>
+        <v>0.6972</v>
       </c>
       <c r="J33" t="n">
-        <v>16.9048</v>
+        <v>15.3384</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.41</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4478</v>
       </c>
       <c r="J34" t="n">
-        <v>11.2552</v>
+        <v>9.851599999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.22</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3057</v>
+        <v>0.256</v>
       </c>
       <c r="J35" t="n">
-        <v>6.7254</v>
+        <v>5.632</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1175</v>
+        <v>-0.1028</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.585</v>
+        <v>-2.2616</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.02</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1125</v>
+        <v>0.107</v>
       </c>
       <c r="J37" t="n">
-        <v>2.475</v>
+        <v>2.354</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.86</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1644</v>
+        <v>-0.1488</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.6168</v>
+        <v>-3.2736</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2072</v>
+        <v>-0.1917</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.5584</v>
+        <v>-4.2174</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.76</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2665</v>
+        <v>-0.2512</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.863</v>
+        <v>-5.5264</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.21</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7457</v>
+        <v>-0.7884</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.4054</v>
+        <v>-17.3448</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.7</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1318</v>
+        <v>1.1013</v>
       </c>
       <c r="J42" t="n">
-        <v>31.6904</v>
+        <v>30.8364</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2744</v>
+        <v>0.2294</v>
       </c>
       <c r="J43" t="n">
-        <v>7.6832</v>
+        <v>6.4232</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0534</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.8928</v>
+        <v>-1.4952</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.96</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0822</v>
+        <v>-0.0664</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.3016</v>
+        <v>-1.8592</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2013</v>
+        <v>-0.181</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.6364</v>
+        <v>-5.068</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1344</v>
+        <v>1.1452</v>
       </c>
       <c r="J47" t="n">
-        <v>31.7632</v>
+        <v>32.0656</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.382</v>
+        <v>0.3408</v>
       </c>
       <c r="J48" t="n">
-        <v>10.696</v>
+        <v>9.542400000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3567</v>
+        <v>0.3161</v>
       </c>
       <c r="J49" t="n">
-        <v>9.9876</v>
+        <v>8.8508</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4299</v>
+        <v>-0.3869</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.0372</v>
+        <v>-10.8332</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8407</v>
+        <v>-0.8203</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.5396</v>
+        <v>-22.9684</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.28</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6672</v>
+        <v>0.6523</v>
       </c>
       <c r="J52" t="n">
-        <v>17.3472</v>
+        <v>16.9598</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2216</v>
+        <v>0.188</v>
       </c>
       <c r="J53" t="n">
-        <v>5.7616</v>
+        <v>4.888</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="J54" t="n">
-        <v>2.4128</v>
+        <v>1.898</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="J55" t="n">
-        <v>2.4128</v>
+        <v>1.898</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3791</v>
+        <v>-0.3361</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.8566</v>
+        <v>-8.7386</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4707</v>
+        <v>0.4236</v>
       </c>
       <c r="J57" t="n">
-        <v>12.2382</v>
+        <v>11.0136</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.21</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4312</v>
+        <v>0.3764</v>
       </c>
       <c r="J58" t="n">
-        <v>11.2112</v>
+        <v>9.7864</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2778</v>
+        <v>0.231</v>
       </c>
       <c r="J59" t="n">
-        <v>7.2228</v>
+        <v>6.006</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.08</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2023</v>
+        <v>0.1637</v>
       </c>
       <c r="J60" t="n">
-        <v>5.2598</v>
+        <v>4.2562</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.289</v>
+        <v>-0.2711</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.514</v>
+        <v>-7.0486</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.69</v>
       </c>
       <c r="I62" t="n">
-        <v>1.205</v>
+        <v>1.2028</v>
       </c>
       <c r="J62" t="n">
-        <v>31.33</v>
+        <v>31.2728</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.29</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6532</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>16.9832</v>
+        <v>16.6816</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5777</v>
+        <v>0.5699</v>
       </c>
       <c r="J64" t="n">
-        <v>15.0202</v>
+        <v>14.8174</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0374</v>
+        <v>-0.0319</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.9724</v>
+        <v>-0.8294</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4103</v>
+        <v>-0.3698</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.6678</v>
+        <v>-9.614800000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.01</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0683</v>
+        <v>0.0492</v>
       </c>
       <c r="J67" t="n">
-        <v>1.7758</v>
+        <v>1.2792</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0464</v>
+        <v>-0.0371</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.2064</v>
+        <v>-0.9646</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0883</v>
+        <v>-0.075</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.2958</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1794</v>
+        <v>-0.1612</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.6644</v>
+        <v>-4.1912</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.53</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4858</v>
+        <v>-0.4838</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.6308</v>
+        <v>-12.5788</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.03</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1183</v>
+        <v>0.0883</v>
       </c>
       <c r="J72" t="n">
-        <v>3.4307</v>
+        <v>2.5607</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.96</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0653</v>
+        <v>-0.0538</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.8937</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1166</v>
+        <v>-0.1006</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.3814</v>
+        <v>-2.9174</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.9706</v>
+        <v>-4.4225</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3287</v>
+        <v>-0.3122</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.532299999999999</v>
+        <v>-9.053800000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9843</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>28.5447</v>
+        <v>28.1677</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7156</v>
       </c>
       <c r="J78" t="n">
-        <v>21.1787</v>
+        <v>20.7524</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.21</v>
       </c>
       <c r="I79" t="n">
-        <v>0.533</v>
+        <v>0.5253</v>
       </c>
       <c r="J79" t="n">
-        <v>15.457</v>
+        <v>15.2337</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4688</v>
+        <v>0.4449</v>
       </c>
       <c r="J80" t="n">
-        <v>13.5952</v>
+        <v>12.9021</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7154</v>
+        <v>-0.6878</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.7466</v>
+        <v>-19.9462</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.96</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0437</v>
+        <v>-0.0321</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.0488</v>
+        <v>-0.7704</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2</v>
+        <v>-0.1842</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.8</v>
+        <v>-4.4208</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.77</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2593</v>
+        <v>-0.2432</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.2232</v>
+        <v>-5.8368</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.66</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.359</v>
+        <v>-0.345</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.616</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4482</v>
+        <v>-0.441</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.7568</v>
+        <v>-10.584</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9105</v>
+        <v>0.897</v>
       </c>
       <c r="J87" t="n">
-        <v>21.852</v>
+        <v>21.528</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.38</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7732</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>18.5568</v>
+        <v>18.2544</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6605</v>
+        <v>0.6514</v>
       </c>
       <c r="J89" t="n">
-        <v>15.852</v>
+        <v>15.6336</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.25</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5865</v>
+        <v>0.581</v>
       </c>
       <c r="J90" t="n">
-        <v>14.076</v>
+        <v>13.944</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3192</v>
+        <v>0.2873</v>
       </c>
       <c r="J91" t="n">
-        <v>7.6608</v>
+        <v>6.8952</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6575</v>
       </c>
       <c r="J92" t="n">
-        <v>23.494</v>
+        <v>22.355</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3488</v>
+        <v>0.311</v>
       </c>
       <c r="J93" t="n">
-        <v>11.8592</v>
+        <v>10.574</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2983</v>
+        <v>0.2626</v>
       </c>
       <c r="J94" t="n">
-        <v>10.1422</v>
+        <v>8.9284</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2156</v>
+        <v>0.1846</v>
       </c>
       <c r="J95" t="n">
-        <v>7.3304</v>
+        <v>6.2764</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0164</v>
+        <v>-0.0117</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.5576</v>
+        <v>-0.3978</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.07</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1922</v>
+        <v>0.1522</v>
       </c>
       <c r="J97" t="n">
-        <v>6.5348</v>
+        <v>5.1748</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.04</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1251</v>
+        <v>0.0946</v>
       </c>
       <c r="J98" t="n">
-        <v>4.2534</v>
+        <v>3.2164</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0437</v>
+        <v>0.0295</v>
       </c>
       <c r="J99" t="n">
-        <v>1.4858</v>
+        <v>1.003</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0987</v>
+        <v>-0.082</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.3558</v>
+        <v>-2.788</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1233</v>
+        <v>-0.1048</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.1922</v>
+        <v>-3.5632</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.6</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2262</v>
+        <v>1.2421</v>
       </c>
       <c r="J102" t="n">
-        <v>33.1074</v>
+        <v>33.5367</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0052</v>
+        <v>1.0042</v>
       </c>
       <c r="J103" t="n">
-        <v>27.1404</v>
+        <v>27.1134</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5603</v>
+        <v>0.5293</v>
       </c>
       <c r="J104" t="n">
-        <v>15.1281</v>
+        <v>14.2911</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1596</v>
+        <v>0.1337</v>
       </c>
       <c r="J105" t="n">
-        <v>4.3092</v>
+        <v>3.6099</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1034</v>
+        <v>-0.083</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.7918</v>
+        <v>-2.241</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.06</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2057</v>
+        <v>0.1658</v>
       </c>
       <c r="J107" t="n">
-        <v>5.5539</v>
+        <v>4.4766</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1045</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>2.8215</v>
+        <v>2.1249</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1784</v>
+        <v>-0.1608</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.8168</v>
+        <v>-4.3416</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.74</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2951</v>
+        <v>-0.2772</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.9677</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4754</v>
+        <v>-0.4719</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.8358</v>
+        <v>-12.7413</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.93</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0324</v>
+        <v>-0.004</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.5508</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1468</v>
+        <v>-0.1247</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.4956</v>
+        <v>-2.1199</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.48</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.494</v>
+        <v>-0.4919</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.398</v>
+        <v>-8.362299999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.35</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6091</v>
+        <v>-0.6216</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.3547</v>
+        <v>-10.5672</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.28</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6713</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.4121</v>
+        <v>-11.8167</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.57</v>
       </c>
       <c r="I117" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J117" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3717</v>
+        <v>1.3984</v>
       </c>
       <c r="J118" t="n">
-        <v>23.3189</v>
+        <v>23.7728</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.31</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7043</v>
       </c>
       <c r="J119" t="n">
-        <v>12.2451</v>
+        <v>11.9731</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5117</v>
+        <v>0.4826</v>
       </c>
       <c r="J120" t="n">
-        <v>8.6989</v>
+        <v>8.2042</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.14</v>
       </c>
       <c r="I121" t="n">
-        <v>0.351</v>
+        <v>0.316</v>
       </c>
       <c r="J121" t="n">
-        <v>5.967</v>
+        <v>5.372</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4349</v>
+        <v>0.3707</v>
       </c>
       <c r="J122" t="n">
-        <v>12.6121</v>
+        <v>10.7503</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.27</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3793</v>
+        <v>0.3192</v>
       </c>
       <c r="J123" t="n">
-        <v>10.9997</v>
+        <v>9.2568</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3793</v>
+        <v>0.3192</v>
       </c>
       <c r="J124" t="n">
-        <v>10.9997</v>
+        <v>9.2568</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2377</v>
+        <v>0.1925</v>
       </c>
       <c r="J125" t="n">
-        <v>6.8933</v>
+        <v>5.5825</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0146</v>
+        <v>-0.012</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.4234</v>
+        <v>-0.348</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3529</v>
+        <v>0.3461</v>
       </c>
       <c r="J127" t="n">
-        <v>10.2341</v>
+        <v>10.0369</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3392</v>
+        <v>0.331</v>
       </c>
       <c r="J128" t="n">
-        <v>9.8368</v>
+        <v>9.599</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.1001</v>
+        <v>-2.6303</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2563</v>
+        <v>-0.2366</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.4327</v>
+        <v>-6.8614</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4579</v>
+        <v>-0.4534</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.2791</v>
+        <v>-13.1486</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.15</v>
       </c>
       <c r="I132" t="n">
-        <v>0.368</v>
+        <v>0.3142</v>
       </c>
       <c r="J132" t="n">
-        <v>8.464</v>
+        <v>7.2266</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0186</v>
+        <v>-0.0137</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.4278</v>
+        <v>-0.3151</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.4311</v>
+        <v>-2.0723</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2441</v>
+        <v>-0.2243</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.6143</v>
+        <v>-5.1589</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3486</v>
+        <v>-0.3334</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.017799999999999</v>
+        <v>-7.6682</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.56</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1607</v>
+        <v>1.1747</v>
       </c>
       <c r="J137" t="n">
-        <v>26.6961</v>
+        <v>27.0181</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.45</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0094</v>
+        <v>1.0111</v>
       </c>
       <c r="J138" t="n">
-        <v>23.2162</v>
+        <v>23.2553</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.39</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9065</v>
+        <v>0.8949</v>
       </c>
       <c r="J139" t="n">
-        <v>20.8495</v>
+        <v>20.5827</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3659</v>
+        <v>0.3339</v>
       </c>
       <c r="J140" t="n">
-        <v>8.415699999999999</v>
+        <v>7.6797</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2898</v>
+        <v>0.2582</v>
       </c>
       <c r="J141" t="n">
-        <v>6.6654</v>
+        <v>5.9386</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.32</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4659</v>
+        <v>0.3997</v>
       </c>
       <c r="J142" t="n">
-        <v>13.977</v>
+        <v>11.991</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.17</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2827</v>
+        <v>0.2285</v>
       </c>
       <c r="J143" t="n">
-        <v>8.481</v>
+        <v>6.855</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0586</v>
+        <v>-0.0459</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.758</v>
+        <v>-1.377</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2124</v>
+        <v>-0.1918</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.372</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3204</v>
+        <v>-0.3037</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.612</v>
+        <v>-9.111000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9799</v>
+        <v>1.0717</v>
       </c>
       <c r="J147" t="n">
-        <v>29.397</v>
+        <v>32.151</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5528</v>
+        <v>0.5692</v>
       </c>
       <c r="J148" t="n">
-        <v>16.584</v>
+        <v>17.076</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3903</v>
+        <v>0.3881</v>
       </c>
       <c r="J149" t="n">
-        <v>11.709</v>
+        <v>11.643</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3058</v>
+        <v>-0.2899</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.173999999999999</v>
+        <v>-8.696999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.66</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3975</v>
+        <v>-0.3892</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.925</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.87</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1439</v>
+        <v>-0.1276</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.878</v>
+        <v>-2.552</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1553</v>
+        <v>-0.1392</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.106</v>
+        <v>-2.784</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.65</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.36</v>
+        <v>-0.3476</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.2</v>
+        <v>-6.952</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4397</v>
+        <v>-0.4318</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.794</v>
+        <v>-8.635999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4925</v>
+        <v>-0.4898</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.85</v>
+        <v>-9.795999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.68</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2971</v>
+        <v>1.3171</v>
       </c>
       <c r="J157" t="n">
-        <v>25.942</v>
+        <v>26.342</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2092</v>
+        <v>1.2265</v>
       </c>
       <c r="J158" t="n">
-        <v>24.184</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0407</v>
+        <v>1.0509</v>
       </c>
       <c r="J159" t="n">
-        <v>20.814</v>
+        <v>21.018</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.24</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5998</v>
+        <v>0.575</v>
       </c>
       <c r="J160" t="n">
-        <v>11.996</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.14</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3744</v>
+        <v>0.3422</v>
       </c>
       <c r="J161" t="n">
-        <v>7.488</v>
+        <v>6.844</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.17</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4022</v>
+        <v>0.3469</v>
       </c>
       <c r="J162" t="n">
-        <v>10.055</v>
+        <v>8.672499999999999</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3657</v>
+        <v>0.3118</v>
       </c>
       <c r="J163" t="n">
-        <v>9.1425</v>
+        <v>7.795</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0194</v>
+        <v>-0.0144</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.485</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.73</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3123</v>
+        <v>-0.2948</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.8075</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4652</v>
+        <v>-0.4613</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.63</v>
+        <v>-11.5325</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8581</v>
+        <v>0.8361</v>
       </c>
       <c r="J167" t="n">
-        <v>21.4525</v>
+        <v>20.9025</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.07</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2445</v>
+        <v>0.2115</v>
       </c>
       <c r="J168" t="n">
-        <v>6.1125</v>
+        <v>5.2875</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.186</v>
+        <v>0.1573</v>
       </c>
       <c r="J169" t="n">
-        <v>4.65</v>
+        <v>3.9325</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.03</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1212</v>
+        <v>0.0988</v>
       </c>
       <c r="J170" t="n">
-        <v>3.03</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.02</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0848</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>2.12</v>
+        <v>1.6775</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9005</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>27.015</v>
+        <v>26.508</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2239</v>
+        <v>0.1892</v>
       </c>
       <c r="J173" t="n">
-        <v>6.717</v>
+        <v>5.676</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.01</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0546</v>
+        <v>0.0408</v>
       </c>
       <c r="J174" t="n">
-        <v>1.638</v>
+        <v>1.224</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1751</v>
+        <v>-0.1421</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.253</v>
+        <v>-4.263</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5949</v>
+        <v>-0.5562</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.847</v>
+        <v>-16.686</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.37</v>
       </c>
       <c r="I177" t="n">
-        <v>0.704</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>21.12</v>
+        <v>19.431</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1692</v>
+        <v>0.1323</v>
       </c>
       <c r="J178" t="n">
-        <v>5.076</v>
+        <v>3.969</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1241</v>
+        <v>-0.1055</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.723</v>
+        <v>-3.165</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1914</v>
+        <v>-0.1708</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.742</v>
+        <v>-5.124</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2329</v>
+        <v>-0.2126</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.987</v>
+        <v>-6.378</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2511</v>
+        <v>1.2681</v>
       </c>
       <c r="J182" t="n">
-        <v>32.5286</v>
+        <v>32.9706</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6021</v>
+        <v>0.5724</v>
       </c>
       <c r="J183" t="n">
-        <v>15.6546</v>
+        <v>14.8824</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.21</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5595</v>
+        <v>0.5288</v>
       </c>
       <c r="J184" t="n">
-        <v>14.547</v>
+        <v>13.7488</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5377</v>
+        <v>0.5065</v>
       </c>
       <c r="J185" t="n">
-        <v>13.9802</v>
+        <v>13.169</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="J186" t="n">
-        <v>4.9114</v>
+        <v>4.1912</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3089</v>
+        <v>0.2604</v>
       </c>
       <c r="J187" t="n">
-        <v>8.0314</v>
+        <v>6.7704</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0112</v>
+        <v>-0.0069</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.2912</v>
+        <v>-0.1794</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.86</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1791</v>
+        <v>-0.1611</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.6566</v>
+        <v>-4.1886</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.66</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.37</v>
+        <v>-0.3562</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.261200000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.65</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3791</v>
+        <v>-0.3659</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.8566</v>
+        <v>-9.513400000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.94</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6333</v>
+        <v>1.6772</v>
       </c>
       <c r="J192" t="n">
-        <v>37.5659</v>
+        <v>38.5756</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.47</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0371</v>
+        <v>1.0435</v>
       </c>
       <c r="J193" t="n">
-        <v>23.8533</v>
+        <v>24.0005</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.29</v>
       </c>
       <c r="I194" t="n">
-        <v>0.715</v>
+        <v>0.6931</v>
       </c>
       <c r="J194" t="n">
-        <v>16.445</v>
+        <v>15.9413</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.1</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2872</v>
+        <v>0.2556</v>
       </c>
       <c r="J195" t="n">
-        <v>6.6056</v>
+        <v>5.8788</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3764</v>
+        <v>-0.3394</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.6572</v>
+        <v>-7.8062</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1273</v>
+        <v>0.0968</v>
       </c>
       <c r="J197" t="n">
-        <v>2.9279</v>
+        <v>2.2264</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.98</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0304</v>
+        <v>-0.0232</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.6992</v>
+        <v>-0.5336</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.93</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.101</v>
+        <v>-0.0868</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.323</v>
+        <v>-1.9964</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.75</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2875</v>
+        <v>-0.2692</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.6125</v>
+        <v>-6.1916</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4068</v>
+        <v>-0.3961</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.356400000000001</v>
+        <v>-9.110300000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2415</v>
+        <v>1.2581</v>
       </c>
       <c r="J202" t="n">
-        <v>31.0375</v>
+        <v>31.4525</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.25</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6446</v>
+        <v>0.6153</v>
       </c>
       <c r="J203" t="n">
-        <v>16.115</v>
+        <v>15.3825</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5399</v>
+        <v>0.5081</v>
       </c>
       <c r="J204" t="n">
-        <v>13.4975</v>
+        <v>12.7025</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4499</v>
+        <v>0.417</v>
       </c>
       <c r="J205" t="n">
-        <v>11.2475</v>
+        <v>10.425</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.02</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0594</v>
+        <v>0.0431</v>
       </c>
       <c r="J206" t="n">
-        <v>1.485</v>
+        <v>1.0775</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4101</v>
+        <v>0.3556</v>
       </c>
       <c r="J207" t="n">
-        <v>10.2525</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3356</v>
+        <v>0.2839</v>
       </c>
       <c r="J208" t="n">
-        <v>8.390000000000001</v>
+        <v>7.0975</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1816</v>
+        <v>-0.1625</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.54</v>
+        <v>-4.0625</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2716</v>
+        <v>-0.2526</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.79</v>
+        <v>-6.315</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.54</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4802</v>
+        <v>-0.4778</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.005</v>
+        <v>-11.945</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.28</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7227</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>18.7902</v>
+        <v>17.992</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.21</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5737</v>
+        <v>0.5373</v>
       </c>
       <c r="J213" t="n">
-        <v>14.9162</v>
+        <v>13.9698</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4167</v>
+        <v>0.3797</v>
       </c>
       <c r="J214" t="n">
-        <v>10.8342</v>
+        <v>9.872199999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2373</v>
+        <v>0.2064</v>
       </c>
       <c r="J215" t="n">
-        <v>6.1698</v>
+        <v>5.3664</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.04</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1468</v>
+        <v>0.1223</v>
       </c>
       <c r="J216" t="n">
-        <v>3.8168</v>
+        <v>3.1798</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.49</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9221</v>
+        <v>0.8884</v>
       </c>
       <c r="J217" t="n">
-        <v>23.9746</v>
+        <v>23.0984</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.95</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.08</v>
+        <v>-0.0668</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.08</v>
+        <v>-1.7368</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.86</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1827</v>
+        <v>-0.1633</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.7502</v>
+        <v>-4.2458</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.73</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3111</v>
+        <v>-0.2935</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.0886</v>
+        <v>-7.631</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.51</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5072</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.1872</v>
+        <v>-13.2236</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.02</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0688</v>
+        <v>0.0555</v>
       </c>
       <c r="J222" t="n">
-        <v>1.5136</v>
+        <v>1.221</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.98</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0364</v>
+        <v>-0.0285</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.8008</v>
+        <v>-0.627</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0364</v>
+        <v>-0.0285</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.8008</v>
+        <v>-0.627</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1831</v>
+        <v>-0.1635</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.0282</v>
+        <v>-3.597</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3208</v>
+        <v>-0.3038</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.0576</v>
+        <v>-6.6836</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.57</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6871</v>
+        <v>0.6149</v>
       </c>
       <c r="J227" t="n">
-        <v>15.1162</v>
+        <v>13.5278</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.31</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4191</v>
+        <v>0.357</v>
       </c>
       <c r="J228" t="n">
-        <v>9.2202</v>
+        <v>7.854</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2336</v>
+        <v>0.1896</v>
       </c>
       <c r="J229" t="n">
-        <v>5.1392</v>
+        <v>4.1712</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.14</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2205</v>
+        <v>0.1781</v>
       </c>
       <c r="J230" t="n">
-        <v>4.851</v>
+        <v>3.9182</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.09</v>
       </c>
       <c r="I231" t="n">
-        <v>0.151</v>
+        <v>0.1178</v>
       </c>
       <c r="J231" t="n">
-        <v>3.322</v>
+        <v>2.5916</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0145</v>
+        <v>1.0142</v>
       </c>
       <c r="J232" t="n">
-        <v>29.4205</v>
+        <v>29.4118</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5654</v>
+        <v>0.5323</v>
       </c>
       <c r="J233" t="n">
-        <v>16.3966</v>
+        <v>15.4367</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.18</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4665</v>
       </c>
       <c r="J234" t="n">
-        <v>14.5145</v>
+        <v>13.5285</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.18</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4665</v>
       </c>
       <c r="J235" t="n">
-        <v>14.5145</v>
+        <v>13.5285</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1674</v>
+        <v>0.1414</v>
       </c>
       <c r="J236" t="n">
-        <v>4.8546</v>
+        <v>4.1006</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.12</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3102</v>
+        <v>0.2593</v>
       </c>
       <c r="J237" t="n">
-        <v>8.995799999999999</v>
+        <v>7.5197</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.08</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2297</v>
+        <v>0.1852</v>
       </c>
       <c r="J238" t="n">
-        <v>6.6613</v>
+        <v>5.3708</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1402</v>
+        <v>-0.1222</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.0658</v>
+        <v>-3.5438</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2738</v>
+        <v>-0.2547</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.9402</v>
+        <v>-7.3863</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3306</v>
+        <v>-0.3141</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.587400000000001</v>
+        <v>-9.1089</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4233</v>
+        <v>0.3585</v>
       </c>
       <c r="J242" t="n">
-        <v>15.2388</v>
+        <v>12.906</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1821</v>
+        <v>0.1409</v>
       </c>
       <c r="J243" t="n">
-        <v>6.5556</v>
+        <v>5.0724</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0291</v>
+        <v>0.0192</v>
       </c>
       <c r="J244" t="n">
-        <v>1.0476</v>
+        <v>0.6912</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.93</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1153</v>
+        <v>-0.097</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.1508</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1509</v>
+        <v>-0.1309</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.4324</v>
+        <v>-4.7124</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4116</v>
+        <v>0.41</v>
       </c>
       <c r="J247" t="n">
-        <v>14.8176</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3745</v>
+        <v>0.3693</v>
       </c>
       <c r="J248" t="n">
-        <v>13.482</v>
+        <v>13.2948</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.05</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1072</v>
+        <v>0.0946</v>
       </c>
       <c r="J249" t="n">
-        <v>3.8592</v>
+        <v>3.4056</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.03</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0697</v>
+        <v>0.0593</v>
       </c>
       <c r="J250" t="n">
-        <v>2.5092</v>
+        <v>2.1348</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1077</v>
+        <v>-0.0898</v>
       </c>
       <c r="J251" t="n">
-        <v>-3.8772</v>
+        <v>-3.2328</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.18</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4282</v>
+        <v>0.3732</v>
       </c>
       <c r="J252" t="n">
-        <v>10.2768</v>
+        <v>8.956799999999999</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1687</v>
+        <v>0.1314</v>
       </c>
       <c r="J253" t="n">
-        <v>4.0488</v>
+        <v>3.1536</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.92</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1163</v>
+        <v>-0.1004</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.7912</v>
+        <v>-2.4096</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.72</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.319</v>
+        <v>-0.3019</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.656</v>
+        <v>-7.2456</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4278</v>
+        <v>-0.4193</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.2672</v>
+        <v>-10.0632</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.72</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3779</v>
+        <v>1.402</v>
       </c>
       <c r="J257" t="n">
-        <v>33.0696</v>
+        <v>33.648</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.37</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8771</v>
+        <v>0.8608</v>
       </c>
       <c r="J258" t="n">
-        <v>21.0504</v>
+        <v>20.6592</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.17</v>
       </c>
       <c r="I259" t="n">
-        <v>0.469</v>
+        <v>0.4371</v>
       </c>
       <c r="J259" t="n">
-        <v>11.256</v>
+        <v>10.4904</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2716</v>
+        <v>0.2406</v>
       </c>
       <c r="J260" t="n">
-        <v>6.5184</v>
+        <v>5.7744</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.02</v>
       </c>
       <c r="I261" t="n">
-        <v>0.055</v>
+        <v>0.0386</v>
       </c>
       <c r="J261" t="n">
-        <v>1.32</v>
+        <v>0.9264</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.27</v>
       </c>
       <c r="I262" t="n">
-        <v>0.5856</v>
+        <v>0.5316</v>
       </c>
       <c r="J262" t="n">
-        <v>15.2256</v>
+        <v>13.8216</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0931</v>
+        <v>0.0678</v>
       </c>
       <c r="J263" t="n">
-        <v>2.4206</v>
+        <v>1.7628</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.98</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0338</v>
+        <v>-0.0262</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.8788</v>
+        <v>-0.6812</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.7</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.337</v>
+        <v>-0.3209</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.762</v>
+        <v>-8.343400000000001</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.47</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5395</v>
+        <v>-0.5454</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.027</v>
+        <v>-14.1804</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.52</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1186</v>
+        <v>1.1309</v>
       </c>
       <c r="J267" t="n">
-        <v>29.0836</v>
+        <v>29.4034</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9034</v>
       </c>
       <c r="J268" t="n">
-        <v>23.8368</v>
+        <v>23.4884</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.26</v>
       </c>
       <c r="I269" t="n">
-        <v>0.6635</v>
+        <v>0.6357</v>
       </c>
       <c r="J269" t="n">
-        <v>17.251</v>
+        <v>16.5282</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.09</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2733</v>
+        <v>0.2422</v>
       </c>
       <c r="J270" t="n">
-        <v>7.1058</v>
+        <v>6.2972</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.06</v>
       </c>
       <c r="I271" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="J271" t="n">
-        <v>4.9114</v>
+        <v>4.1912</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.85</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5171</v>
+        <v>1.5501</v>
       </c>
       <c r="J272" t="n">
-        <v>33.3762</v>
+        <v>34.1022</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.52</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1012</v>
+        <v>1.1148</v>
       </c>
       <c r="J273" t="n">
-        <v>24.2264</v>
+        <v>24.5256</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.3</v>
       </c>
       <c r="I274" t="n">
-        <v>0.731</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J274" t="n">
-        <v>16.082</v>
+        <v>15.6464</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.17</v>
       </c>
       <c r="I275" t="n">
-        <v>0.454</v>
+        <v>0.4233</v>
       </c>
       <c r="J275" t="n">
-        <v>9.988</v>
+        <v>9.3126</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>0.0394</v>
+        <v>0.0213</v>
       </c>
       <c r="J276" t="n">
-        <v>0.8668</v>
+        <v>0.4686</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.03</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1679</v>
+        <v>0.141</v>
       </c>
       <c r="J277" t="n">
-        <v>3.6938</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.77</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2581</v>
+        <v>-0.2425</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.6782</v>
+        <v>-5.335</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.72</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3033</v>
+        <v>-0.2878</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.6726</v>
+        <v>-6.3316</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.67</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3486</v>
+        <v>-0.3343</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.6692</v>
+        <v>-7.3546</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.53</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4732</v>
+        <v>-0.4686</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.4104</v>
+        <v>-10.3092</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.58</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1828</v>
+        <v>1.1978</v>
       </c>
       <c r="J282" t="n">
-        <v>24.8388</v>
+        <v>25.1538</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.53</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1175</v>
+        <v>1.1311</v>
       </c>
       <c r="J283" t="n">
-        <v>23.4675</v>
+        <v>23.7531</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.35</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8294</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J284" t="n">
-        <v>17.4174</v>
+        <v>17.094</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.17</v>
       </c>
       <c r="I285" t="n">
-        <v>0.4573</v>
+        <v>0.4266</v>
       </c>
       <c r="J285" t="n">
-        <v>9.603300000000001</v>
+        <v>8.958600000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.12</v>
       </c>
       <c r="I286" t="n">
-        <v>0.3373</v>
+        <v>0.3053</v>
       </c>
       <c r="J286" t="n">
-        <v>7.0833</v>
+        <v>6.4113</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.95</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0478</v>
+        <v>-0.0336</v>
       </c>
       <c r="J287" t="n">
-        <v>-1.0038</v>
+        <v>-0.7056</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1927</v>
+        <v>-0.1773</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.0467</v>
+        <v>-3.7233</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.73</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2919</v>
+        <v>-0.2775</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.1299</v>
+        <v>-5.8275</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4425</v>
+        <v>-0.4348</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.2925</v>
+        <v>-9.130800000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5128</v>
+        <v>-0.5127</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.7688</v>
+        <v>-10.7667</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2875</v>
+        <v>1.3094</v>
       </c>
       <c r="J292" t="n">
-        <v>37.3375</v>
+        <v>37.9726</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.39</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.9383</v>
       </c>
       <c r="J293" t="n">
-        <v>27.5529</v>
+        <v>27.2107</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3952</v>
+        <v>0.3574</v>
       </c>
       <c r="J294" t="n">
-        <v>11.4608</v>
+        <v>10.3646</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.84</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5178</v>
+        <v>-0.4773</v>
       </c>
       <c r="J295" t="n">
-        <v>-15.0162</v>
+        <v>-13.8417</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.64</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.9576</v>
+        <v>-0.952</v>
       </c>
       <c r="J296" t="n">
-        <v>-27.7704</v>
+        <v>-27.608</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.26</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5208</v>
+        <v>0.4613</v>
       </c>
       <c r="J297" t="n">
-        <v>15.1032</v>
+        <v>13.3777</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.24</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4886</v>
+        <v>0.4296</v>
       </c>
       <c r="J298" t="n">
-        <v>14.1694</v>
+        <v>12.4584</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.11</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2633</v>
+        <v>0.217</v>
       </c>
       <c r="J299" t="n">
-        <v>7.6357</v>
+        <v>6.293</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.87</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1847</v>
+        <v>-0.1641</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.3563</v>
+        <v>-4.7589</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2767</v>
+        <v>-0.2579</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.0243</v>
+        <v>-7.4791</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0089</v>
+        <v>0.0065</v>
       </c>
       <c r="J302" t="n">
-        <v>0.2403</v>
+        <v>0.1755</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0192</v>
+        <v>-0.0142</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.5184</v>
+        <v>-0.3834</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.96</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0673</v>
+        <v>-0.0552</v>
       </c>
       <c r="J304" t="n">
-        <v>-1.8171</v>
+        <v>-1.4904</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.91</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1291</v>
+        <v>-0.1118</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.4857</v>
+        <v>-3.0186</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3121</v>
+        <v>-0.2946</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.4267</v>
+        <v>-7.9542</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.75</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8721</v>
+        <v>0.8044</v>
       </c>
       <c r="J307" t="n">
-        <v>23.5467</v>
+        <v>21.7188</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.29</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4024</v>
+        <v>0.3403</v>
       </c>
       <c r="J308" t="n">
-        <v>10.8648</v>
+        <v>9.1881</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.11</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1847</v>
+        <v>0.1463</v>
       </c>
       <c r="J309" t="n">
-        <v>4.9869</v>
+        <v>3.9501</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.0141</v>
+        <v>-0.0116</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.3807</v>
+        <v>-0.3132</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.83</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2383</v>
+        <v>-0.2194</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.4341</v>
+        <v>-5.9238</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.33</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8521</v>
+        <v>0.83</v>
       </c>
       <c r="J312" t="n">
-        <v>24.7109</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.22</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6163</v>
+        <v>0.5784</v>
       </c>
       <c r="J313" t="n">
-        <v>17.8727</v>
+        <v>16.7736</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.16</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4786</v>
+        <v>0.4371</v>
       </c>
       <c r="J314" t="n">
-        <v>13.8794</v>
+        <v>12.6759</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.96</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1788</v>
+        <v>-0.1452</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.1852</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.0073</v>
+        <v>-1.0059</v>
       </c>
       <c r="J316" t="n">
-        <v>-29.2117</v>
+        <v>-29.1711</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3997</v>
+        <v>0.3434</v>
       </c>
       <c r="J317" t="n">
-        <v>11.5913</v>
+        <v>9.958600000000001</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.233</v>
+        <v>0.1884</v>
       </c>
       <c r="J318" t="n">
-        <v>6.757</v>
+        <v>5.4636</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0859</v>
+        <v>-0.0703</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.4911</v>
+        <v>-2.0387</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.93</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1113</v>
+        <v>-0.0936</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.2277</v>
+        <v>-2.7144</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.84</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2117</v>
+        <v>-0.1911</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.1393</v>
+        <v>-5.5419</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.16</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3829</v>
+        <v>0.3282</v>
       </c>
       <c r="J322" t="n">
-        <v>10.3383</v>
+        <v>8.8614</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.96</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.0678</v>
+        <v>-0.0556</v>
       </c>
       <c r="J323" t="n">
-        <v>-1.8306</v>
+        <v>-1.5012</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0793</v>
       </c>
       <c r="J324" t="n">
-        <v>-2.5434</v>
+        <v>-2.1411</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2152</v>
+        <v>-0.195</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.8104</v>
+        <v>-5.265</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.73</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3127</v>
+        <v>-0.2952</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.4429</v>
+        <v>-7.9704</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.56</v>
       </c>
       <c r="I327" t="n">
-        <v>1.1809</v>
+        <v>1.195</v>
       </c>
       <c r="J327" t="n">
-        <v>31.8843</v>
+        <v>32.265</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.35</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8481</v>
+        <v>0.8278</v>
       </c>
       <c r="J328" t="n">
-        <v>22.8987</v>
+        <v>22.3506</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.07</v>
       </c>
       <c r="I329" t="n">
-        <v>0.225</v>
+        <v>0.1956</v>
       </c>
       <c r="J329" t="n">
-        <v>6.075</v>
+        <v>5.2812</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.07</v>
       </c>
       <c r="I330" t="n">
-        <v>0.225</v>
+        <v>0.1956</v>
       </c>
       <c r="J330" t="n">
-        <v>6.075</v>
+        <v>5.2812</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.06</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1959</v>
+        <v>0.1681</v>
       </c>
       <c r="J331" t="n">
-        <v>5.2893</v>
+        <v>4.5387</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.34</v>
       </c>
       <c r="I332" t="n">
-        <v>0.648</v>
+        <v>0.5891</v>
       </c>
       <c r="J332" t="n">
-        <v>26.568</v>
+        <v>24.1531</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3381</v>
+        <v>0.2855</v>
       </c>
       <c r="J333" t="n">
-        <v>13.8621</v>
+        <v>11.7055</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.91</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.139</v>
+        <v>-0.1195</v>
       </c>
       <c r="J334" t="n">
-        <v>-5.699</v>
+        <v>-4.8995</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.91</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.139</v>
+        <v>-0.1195</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.699</v>
+        <v>-4.8995</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.9</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1505</v>
+        <v>-0.1306</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.1705</v>
+        <v>-5.3546</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.18</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5295</v>
+        <v>0.4885</v>
       </c>
       <c r="J337" t="n">
-        <v>21.7095</v>
+        <v>20.0285</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I338" t="n">
-        <v>0.4824</v>
+        <v>0.4405</v>
       </c>
       <c r="J338" t="n">
-        <v>19.7784</v>
+        <v>18.0605</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.16</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4824</v>
+        <v>0.4405</v>
       </c>
       <c r="J339" t="n">
-        <v>19.7784</v>
+        <v>18.0605</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2672</v>
+        <v>-0.2275</v>
       </c>
       <c r="J340" t="n">
-        <v>-10.9552</v>
+        <v>-9.327500000000001</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.77</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.664</v>
+        <v>-0.6291</v>
       </c>
       <c r="J341" t="n">
-        <v>-27.224</v>
+        <v>-25.7931</v>
       </c>
     </row>
   </sheetData>
